--- a/docs/snapshot/downloads/pipc.xlsx
+++ b/docs/snapshot/downloads/pipc.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K38"/>
+  <dimension ref="A1:K39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,32 +476,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>11221</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
+          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -511,7 +511,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -521,44 +521,44 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>9501</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>인프라표준화팀</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -578,44 +578,44 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>9381</t>
+          <t>9501</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
+          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>인프라표준화팀</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -635,39 +635,39 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>9271</t>
+          <t>9381</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
+          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>법무감사담당관</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -677,116 +677,116 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>303</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6541</t>
+          <t>9271</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>365</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
+          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>법무감사담당관</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5491</t>
+          <t>6541</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
+          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -796,49 +796,49 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>364</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
+          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>장석인</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -853,49 +853,49 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
+          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>장석인</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -932,27 +932,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
+          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -967,54 +967,54 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>5391</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>363</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
+          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1024,54 +1024,54 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
+          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1081,49 +1081,49 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>362</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
+          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1138,49 +1138,49 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
+          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1217,32 +1217,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
+          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1262,39 +1262,39 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
+          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1319,39 +1319,39 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1376,44 +1376,44 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>561</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
+          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1433,19 +1433,19 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>281</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1455,17 +1455,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
+          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1490,44 +1490,44 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
+          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>98</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1559,27 +1559,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
+          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>924</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1616,27 +1616,27 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
+          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1673,32 +1673,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1708,49 +1708,49 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>743</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>361</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1765,54 +1765,54 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1822,49 +1822,49 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>360</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1879,49 +1879,49 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
+          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1958,27 +1958,27 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AI 범죄 대응 범부처 협의체 출범</t>
+          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2015,32 +2015,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
+          <t>AI 범죄 대응 범부처 협의체 출범</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2050,49 +2050,49 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>359</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2107,49 +2107,49 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
+          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>2754</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2186,32 +2186,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
+          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2221,54 +2221,54 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>7681</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>358</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
+          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>7681</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2300,32 +2300,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>357</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
+          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2357,32 +2357,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>356</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>11169</t>
+          <t>9023</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2414,12 +2414,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>352</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2429,17 +2429,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>13472</t>
+          <t>11169</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2471,27 +2471,27 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>354</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>13472</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2528,55 +2528,112 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>신기술개인정보과</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>9724</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>353</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>「개인정보 처리 방법에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12127</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>전략기획팀</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
         <is>
           <t>11519</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>공지사항</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>

--- a/docs/snapshot/downloads/pipc.xlsx
+++ b/docs/snapshot/downloads/pipc.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K39"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,27 +476,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>11221</t>
+          <t>11392</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>367</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
+          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -511,54 +511,54 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>11391</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>368</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
+          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -568,54 +568,54 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>9501</t>
+          <t>11221</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
+          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>인프라표준화팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -635,19 +635,19 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>9381</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -657,22 +657,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -692,101 +692,101 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>9271</t>
+          <t>9501</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
+          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>법무감사담당관</t>
+          <t>인프라표준화팀</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>6541</t>
+          <t>9381</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
+          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>303</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -806,54 +806,54 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5491</t>
+          <t>9271</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>365</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
+          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>법무감사담당관</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -863,44 +863,44 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>6541</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
+          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>장석인</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -920,34 +920,34 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>364</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
+          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -967,49 +967,49 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
+          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>장석인</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1024,54 +1024,54 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
+          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1091,44 +1091,44 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>5391</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>363</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
+          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1148,44 +1148,44 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
+          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1205,39 +1205,39 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>362</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
+          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1252,54 +1252,54 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
+          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1319,44 +1319,44 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
+          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1376,39 +1376,39 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
+          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1433,44 +1433,44 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1490,44 +1490,44 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>561</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
+          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1547,44 +1547,44 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>281</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
+          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1604,44 +1604,44 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
+          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>98</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1673,27 +1673,27 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
+          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>924</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1730,32 +1730,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
+          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1765,44 +1765,44 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>743</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1844,32 +1844,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>361</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1901,32 +1901,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1958,22 +1958,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>360</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1993,49 +1993,49 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AI 범죄 대응 범부처 협의체 출범</t>
+          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2072,32 +2072,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
+          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2107,54 +2107,54 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
+          <t>AI 범죄 대응 범부처 협의체 출범</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2186,22 +2186,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>359</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2221,54 +2221,54 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
+          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2278,54 +2278,54 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>7681</t>
+          <t>2754</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
+          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2335,44 +2335,44 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>358</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
+          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>7681</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2414,32 +2414,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>357</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>11169</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2471,32 +2471,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>356</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>13472</t>
+          <t>9023</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2528,32 +2528,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>352</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>11169</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2585,55 +2585,169 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>354</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>조사총괄과</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>13472</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>신기술개인정보과</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>9724</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>353</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>「개인정보 처리 방법에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12127</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>전략기획팀</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
         <is>
           <t>11519</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>공지사항</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>

--- a/docs/snapshot/downloads/pipc.xlsx
+++ b/docs/snapshot/downloads/pipc.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:K45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,32 +476,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>11392</t>
+          <t>14451</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>369</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -511,7 +511,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -521,44 +521,44 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>11391</t>
+          <t>14433</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>366</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -578,44 +578,44 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>11221</t>
+          <t>14422</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
+          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -635,44 +635,44 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
+          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -692,44 +692,44 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>9501</t>
+          <t>11392</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>367</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
+          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>인프라표준화팀</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -739,54 +739,54 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>9381</t>
+          <t>11391</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>368</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
+          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -796,111 +796,111 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>9271</t>
+          <t>11221</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
+          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>법무감사담당관</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6541</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -920,44 +920,44 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5491</t>
+          <t>9501</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
+          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>인프라표준화팀</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -967,54 +967,54 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>9381</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
+          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>장석인</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>303</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1034,101 +1034,101 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>9271</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>365</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
+          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>법무감사담당관</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>6541</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
+          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1138,54 +1138,54 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>364</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
+          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1195,54 +1195,54 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
+          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>장석인</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1252,54 +1252,54 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
+          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1319,44 +1319,44 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>5391</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>363</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
+          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1366,54 +1366,54 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
+          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1433,44 +1433,44 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>362</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
+          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1480,54 +1480,54 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
+          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1547,44 +1547,44 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
+          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1604,44 +1604,44 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
+          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1661,44 +1661,44 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1718,44 +1718,44 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>561</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
+          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1775,44 +1775,44 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>281</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
+          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1832,44 +1832,44 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
+          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1879,54 +1879,54 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>98</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
+          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>924</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1958,32 +1958,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
+          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1993,54 +1993,54 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>743</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2072,32 +2072,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>361</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2107,54 +2107,54 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AI 범죄 대응 범부처 협의체 출범</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2186,32 +2186,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>360</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2243,32 +2243,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
+          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2300,32 +2300,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
+          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2357,32 +2357,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
+          <t>AI 범죄 대응 범부처 협의체 출범</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2392,54 +2392,54 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>7681</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>359</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2471,32 +2471,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
+          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2506,54 +2506,54 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>2754</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2563,54 +2563,54 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>11169</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>358</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>13472</t>
+          <t>7681</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2642,32 +2642,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>357</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2699,55 +2699,283 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>356</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>자율보호정책과</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>9023</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>352</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>개인정보보호정책과</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>11169</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>354</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>조사총괄과</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>13472</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>신기술개인정보과</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>9724</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>353</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>「개인정보 처리 방법에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12127</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>전략기획팀</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
         <is>
           <t>11519</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>공지사항</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>

--- a/docs/snapshot/downloads/pipc.xlsx
+++ b/docs/snapshot/downloads/pipc.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K45"/>
+  <dimension ref="A1:K49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,32 +476,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>14451</t>
+          <t>16314</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>370</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
+          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -511,7 +511,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -521,44 +521,44 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>14433</t>
+          <t>16313</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>371</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -578,44 +578,44 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>14422</t>
+          <t>16312</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>372</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
+          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -625,54 +625,54 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>16311</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>373</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
+          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -682,54 +682,54 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>11392</t>
+          <t>14451</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>369</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -749,44 +749,44 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>11391</t>
+          <t>14433</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>366</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -806,44 +806,44 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>11221</t>
+          <t>14422</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
+          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -863,44 +863,44 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
+          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -920,44 +920,44 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>9501</t>
+          <t>11392</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>367</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
+          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>인프라표준화팀</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -967,54 +967,54 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>9381</t>
+          <t>11391</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>368</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
+          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1024,111 +1024,111 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>9271</t>
+          <t>11221</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
+          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>법무감사담당관</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6541</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1148,44 +1148,44 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5491</t>
+          <t>9501</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
+          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>인프라표준화팀</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1195,54 +1195,54 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>9381</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
+          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>장석인</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>303</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1262,101 +1262,101 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>9271</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>365</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
+          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>법무감사담당관</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>6541</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
+          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1366,54 +1366,54 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>364</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
+          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1423,54 +1423,54 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
+          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>장석인</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1480,54 +1480,54 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
+          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1547,44 +1547,44 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>5391</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>363</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
+          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1594,54 +1594,54 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
+          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1661,44 +1661,44 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>362</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
+          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1708,54 +1708,54 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
+          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1775,44 +1775,44 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
+          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1832,44 +1832,44 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
+          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1889,44 +1889,44 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1946,44 +1946,44 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>561</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
+          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2003,44 +2003,44 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>281</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
+          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2060,44 +2060,44 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
+          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2107,54 +2107,54 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>98</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
+          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>924</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2186,32 +2186,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
+          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2221,54 +2221,54 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>743</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2300,32 +2300,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>361</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2335,54 +2335,54 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>AI 범죄 대응 범부처 협의체 출범</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2414,32 +2414,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>360</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2471,32 +2471,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
+          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2528,32 +2528,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
+          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2585,32 +2585,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
+          <t>AI 범죄 대응 범부처 협의체 출범</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2620,54 +2620,54 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>7681</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>359</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2699,32 +2699,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
+          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2734,54 +2734,54 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>2754</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2791,54 +2791,54 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>11169</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>358</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>13472</t>
+          <t>7681</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2870,32 +2870,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>357</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2927,55 +2927,283 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>356</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>자율보호정책과</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>9023</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>352</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>개인정보보호정책과</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>11169</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>354</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>조사총괄과</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>13472</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>신기술개인정보과</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>9724</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>353</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>「개인정보 처리 방법에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12127</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>전략기획팀</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
         <is>
           <t>11519</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>공지사항</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>

--- a/docs/snapshot/downloads/pipc.xlsx
+++ b/docs/snapshot/downloads/pipc.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K49"/>
+  <dimension ref="A1:K52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,32 +476,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>16314</t>
+          <t>16883</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
+          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -511,54 +511,54 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>16313</t>
+          <t>16882</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
+          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -568,54 +568,54 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>16312</t>
+          <t>16881</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
+          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -625,44 +625,44 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>16311</t>
+          <t>16314</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>370</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
+          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -704,32 +704,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>14451</t>
+          <t>16313</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>371</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
+          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -749,44 +749,44 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>14433</t>
+          <t>16312</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>372</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -806,44 +806,44 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>14422</t>
+          <t>16311</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>373</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
+          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -858,39 +858,39 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14451</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>369</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -910,54 +910,54 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>11392</t>
+          <t>14433</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>366</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -977,44 +977,44 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>11391</t>
+          <t>14422</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
+          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1029,49 +1029,49 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>11221</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
+          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1091,44 +1091,44 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>11392</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>367</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
+          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1138,54 +1138,54 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>9501</t>
+          <t>11391</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>368</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
+          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>인프라표준화팀</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1200,49 +1200,49 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>9381</t>
+          <t>11221</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
+          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1262,101 +1262,101 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>9271</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>법무감사담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>6541</t>
+          <t>9501</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
+          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>인프라표준화팀</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1376,44 +1376,44 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5491</t>
+          <t>9381</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
+          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1423,111 +1423,111 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>303</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>9271</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>365</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
+          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>장석인</t>
+          <t>법무감사담당관</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>6541</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
+          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1547,39 +1547,39 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>364</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
+          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1604,44 +1604,44 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
+          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>장석인</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1661,44 +1661,44 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
+          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1708,44 +1708,44 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>5391</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>363</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
+          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1765,54 +1765,54 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
+          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1832,44 +1832,44 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>362</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
+          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1879,54 +1879,54 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
+          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1946,44 +1946,44 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
+          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2003,44 +2003,44 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
+          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2060,56 +2060,56 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>1272</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>운영지원과</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>1269</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>조사1과</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
       <c r="I30" t="inlineStr">
         <is>
           <t>보도자료</t>
@@ -2117,44 +2117,44 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>561</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
+          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2174,44 +2174,44 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>281</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
+          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2231,44 +2231,44 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
+          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>98</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2300,32 +2300,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
+          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2335,54 +2335,54 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>924</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
+          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2414,32 +2414,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2449,54 +2449,54 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>743</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>361</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2506,54 +2506,54 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2585,27 +2585,27 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>360</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AI 범죄 대응 범부처 협의체 출범</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2620,54 +2620,54 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
+          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2677,54 +2677,54 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
+          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2756,32 +2756,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
+          <t>AI 범죄 대응 범부처 협의체 출범</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2813,32 +2813,32 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>359</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>7681</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2870,32 +2870,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
+          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2905,54 +2905,54 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>2754</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
+          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2962,54 +2962,54 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>358</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>11169</t>
+          <t>7681</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3041,32 +3041,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>357</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>13472</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3098,32 +3098,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>356</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>9023</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3155,55 +3155,226 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>352</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>개인정보보호정책과</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>11169</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>354</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>조사총괄과</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>13472</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>신기술개인정보과</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>9724</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>353</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>「개인정보 처리 방법에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12127</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>전략기획팀</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
         <is>
           <t>11519</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>공지사항</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>

--- a/docs/snapshot/downloads/pipc.xlsx
+++ b/docs/snapshot/downloads/pipc.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K52"/>
+  <dimension ref="A1:K53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,27 +476,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>16883</t>
+          <t>17362</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
+          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -511,7 +511,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -521,34 +521,34 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>16882</t>
+          <t>16883</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
+          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -590,27 +590,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>16881</t>
+          <t>16882</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
+          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -647,32 +647,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>16314</t>
+          <t>16881</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
+          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -682,44 +682,44 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>16313</t>
+          <t>16314</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>370</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
+          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -761,22 +761,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>16312</t>
+          <t>16313</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>371</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
+          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -818,22 +818,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>16311</t>
+          <t>16312</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>372</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
+          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -875,32 +875,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>14451</t>
+          <t>16311</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>373</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
+          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -920,39 +920,39 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>14433</t>
+          <t>14451</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>369</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -977,34 +977,34 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>14422</t>
+          <t>14433</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>366</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1024,49 +1024,49 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14422</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
+          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1103,32 +1103,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>11392</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
+          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1138,44 +1138,44 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>11391</t>
+          <t>11392</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>367</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
+          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1217,27 +1217,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>11221</t>
+          <t>11391</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>368</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
+          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1252,54 +1252,54 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>11221</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
+          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1319,44 +1319,44 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>9501</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>인프라표준화팀</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1376,44 +1376,44 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>9381</t>
+          <t>9501</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
+          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>인프라표준화팀</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1433,39 +1433,39 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>9271</t>
+          <t>9381</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
+          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>법무감사담당관</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1475,116 +1475,116 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>303</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6541</t>
+          <t>9271</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>365</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
+          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>법무감사담당관</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5491</t>
+          <t>6541</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
+          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1594,49 +1594,49 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>364</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
+          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>장석인</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1651,49 +1651,49 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
+          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>장석인</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1730,27 +1730,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
+          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1765,54 +1765,54 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>5391</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>363</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
+          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1822,54 +1822,54 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
+          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1879,49 +1879,49 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>362</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
+          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1936,49 +1936,49 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
+          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2015,32 +2015,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
+          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2060,39 +2060,39 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
+          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2117,39 +2117,39 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2174,44 +2174,44 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>561</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
+          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2231,19 +2231,19 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>281</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2253,17 +2253,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
+          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2288,44 +2288,44 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
+          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>98</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2357,27 +2357,27 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
+          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>924</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2414,27 +2414,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
+          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2471,32 +2471,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2506,49 +2506,49 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>743</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>361</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2563,54 +2563,54 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2620,49 +2620,49 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>360</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2677,49 +2677,49 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
+          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2756,27 +2756,27 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AI 범죄 대응 범부처 협의체 출범</t>
+          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2813,32 +2813,32 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
+          <t>AI 범죄 대응 범부처 협의체 출범</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2848,49 +2848,49 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>359</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2905,49 +2905,49 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
+          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>2754</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2984,32 +2984,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
+          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3019,54 +3019,54 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>7681</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>358</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
+          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>7681</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3098,32 +3098,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>357</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
+          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3155,32 +3155,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>356</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>11169</t>
+          <t>9023</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3212,12 +3212,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>352</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3227,17 +3227,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>13472</t>
+          <t>11169</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3269,27 +3269,27 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>354</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>13472</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3326,55 +3326,112 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>신기술개인정보과</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>9724</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>353</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>「개인정보 처리 방법에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12127</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>전략기획팀</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
         <is>
           <t>11519</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>공지사항</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>

--- a/docs/snapshot/downloads/pipc.xlsx
+++ b/docs/snapshot/downloads/pipc.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K53"/>
+  <dimension ref="A1:K54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,32 +476,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>17362</t>
+          <t>17701</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
+          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -511,7 +511,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -521,39 +521,39 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>16883</t>
+          <t>17362</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
+          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -578,34 +578,34 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>16882</t>
+          <t>16883</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
+          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -647,27 +647,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>16881</t>
+          <t>16882</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
+          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -704,32 +704,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>16314</t>
+          <t>16881</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
+          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -739,44 +739,44 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>16313</t>
+          <t>16314</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>370</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
+          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -818,22 +818,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>16312</t>
+          <t>16313</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>371</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
+          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -875,22 +875,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>16311</t>
+          <t>16312</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>372</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
+          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -932,32 +932,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>14451</t>
+          <t>16311</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>373</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
+          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -977,39 +977,39 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>14433</t>
+          <t>14451</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>369</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1034,34 +1034,34 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>14422</t>
+          <t>14433</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>366</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1081,49 +1081,49 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14422</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
+          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1160,32 +1160,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>11392</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
+          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1195,44 +1195,44 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>11391</t>
+          <t>11392</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>367</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
+          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1274,27 +1274,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>11221</t>
+          <t>11391</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>368</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
+          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1309,54 +1309,54 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>11221</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
+          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1376,44 +1376,44 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>9501</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>인프라표준화팀</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1433,44 +1433,44 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>9381</t>
+          <t>9501</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
+          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>인프라표준화팀</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1490,39 +1490,39 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>9271</t>
+          <t>9381</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
+          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>법무감사담당관</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1532,116 +1532,116 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>303</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6541</t>
+          <t>9271</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>365</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
+          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>법무감사담당관</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5491</t>
+          <t>6541</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
+          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1651,49 +1651,49 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>364</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
+          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>장석인</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1708,49 +1708,49 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
+          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>장석인</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1787,27 +1787,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
+          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1822,54 +1822,54 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>5391</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>363</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
+          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1879,54 +1879,54 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
+          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1936,49 +1936,49 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>362</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
+          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1993,49 +1993,49 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
+          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2072,32 +2072,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
+          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2117,39 +2117,39 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
+          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2174,39 +2174,39 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2231,44 +2231,44 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>561</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
+          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2288,19 +2288,19 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>281</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2310,17 +2310,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
+          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2345,44 +2345,44 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
+          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>98</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2414,27 +2414,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
+          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>924</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2471,27 +2471,27 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
+          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2528,32 +2528,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2563,49 +2563,49 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>743</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>361</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2620,54 +2620,54 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2677,49 +2677,49 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>360</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2734,49 +2734,49 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
+          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2813,27 +2813,27 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AI 범죄 대응 범부처 협의체 출범</t>
+          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2870,32 +2870,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
+          <t>AI 범죄 대응 범부처 협의체 출범</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2905,49 +2905,49 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>359</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2962,49 +2962,49 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
+          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>2754</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3041,32 +3041,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
+          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3076,54 +3076,54 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>7681</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>358</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
+          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>7681</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3155,32 +3155,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>357</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
+          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3212,32 +3212,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>356</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>11169</t>
+          <t>9023</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3269,12 +3269,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>352</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3284,17 +3284,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>13472</t>
+          <t>11169</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3326,27 +3326,27 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>354</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>13472</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3383,55 +3383,112 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>신기술개인정보과</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>9724</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>353</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>「개인정보 처리 방법에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12127</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>전략기획팀</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
         <is>
           <t>11519</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>공지사항</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="K54" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>

--- a/docs/snapshot/downloads/pipc.xlsx
+++ b/docs/snapshot/downloads/pipc.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K54"/>
+  <dimension ref="A1:K56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,32 +476,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>17701</t>
+          <t>22391</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>374</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
+          <t>개인정보 영향평가기관 지정갱신 공고</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -511,54 +511,54 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>17362</t>
+          <t>22351</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>374</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
+          <t>개인정보 영향평가기관 지정갱신 공고</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -568,54 +568,54 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>16883</t>
+          <t>17701</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
+          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -635,19 +635,19 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>16882</t>
+          <t>17362</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -657,17 +657,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
+          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -692,39 +692,39 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>16881</t>
+          <t>16883</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
+          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -761,32 +761,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>16314</t>
+          <t>16882</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
+          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -796,54 +796,54 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>16313</t>
+          <t>16881</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
+          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -853,44 +853,44 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>16312</t>
+          <t>16314</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>370</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
+          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -932,22 +932,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>16311</t>
+          <t>16313</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>371</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
+          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -989,32 +989,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>14451</t>
+          <t>16312</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>372</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
+          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1034,44 +1034,44 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>14433</t>
+          <t>16311</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>373</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1091,39 +1091,39 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>14422</t>
+          <t>14451</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>369</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1138,49 +1138,49 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14433</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>366</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1195,54 +1195,54 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>11392</t>
+          <t>14422</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
+          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1252,54 +1252,54 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>11391</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
+          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1309,49 +1309,49 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>11221</t>
+          <t>11392</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>367</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
+          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1366,54 +1366,54 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>11391</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>368</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
+          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1423,54 +1423,54 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>9501</t>
+          <t>11221</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
+          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>인프라표준화팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1490,19 +1490,19 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>9381</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1512,22 +1512,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1547,101 +1547,101 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>9271</t>
+          <t>9501</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
+          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>법무감사담당관</t>
+          <t>인프라표준화팀</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>6541</t>
+          <t>9381</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
+          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>303</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1661,54 +1661,54 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5491</t>
+          <t>9271</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>365</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
+          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>법무감사담당관</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1718,44 +1718,44 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>6541</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
+          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>장석인</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1775,34 +1775,34 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>364</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
+          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1822,49 +1822,49 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
+          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>장석인</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1879,54 +1879,54 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
+          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1946,44 +1946,44 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>5391</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>363</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
+          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2003,44 +2003,44 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
+          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2060,39 +2060,39 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>362</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
+          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2107,54 +2107,54 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
+          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2174,44 +2174,44 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
+          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2231,39 +2231,39 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
+          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2288,44 +2288,44 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2345,44 +2345,44 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>561</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
+          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2402,44 +2402,44 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>281</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
+          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2459,44 +2459,44 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
+          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>98</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2528,27 +2528,27 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
+          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>924</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2585,32 +2585,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
+          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2620,44 +2620,44 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2667,7 +2667,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>743</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2699,32 +2699,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>361</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2756,32 +2756,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2813,22 +2813,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>360</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2848,49 +2848,49 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AI 범죄 대응 범부처 협의체 출범</t>
+          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2927,32 +2927,32 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
+          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2962,54 +2962,54 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
+          <t>AI 범죄 대응 범부처 협의체 출범</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3041,22 +3041,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>359</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3076,54 +3076,54 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
+          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3133,54 +3133,54 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>7681</t>
+          <t>2754</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
+          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3190,44 +3190,44 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>358</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
+          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>7681</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3269,32 +3269,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>357</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>11169</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3326,32 +3326,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>356</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>13472</t>
+          <t>9023</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3383,32 +3383,32 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>352</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>11169</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3440,55 +3440,169 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>354</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>조사총괄과</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>13472</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>신기술개인정보과</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>9724</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>353</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>「개인정보 처리 방법에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12127</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>전략기획팀</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
         <is>
           <t>11519</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>공지사항</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>

--- a/docs/snapshot/downloads/pipc.xlsx
+++ b/docs/snapshot/downloads/pipc.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K56"/>
+  <dimension ref="A1:K57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,32 +476,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>22391</t>
+          <t>22661</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>개인정보 영향평가기관 지정갱신 공고</t>
+          <t>개인정보위, ‘㈜KT의개인정보 유출사고’ 제재처분 의결</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12349</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -511,29 +511,29 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>22351</t>
+          <t>22391</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -578,44 +578,44 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>17701</t>
+          <t>22351</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>374</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
+          <t>개인정보 영향평가기관 지정갱신 공고</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -625,54 +625,54 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>17362</t>
+          <t>17701</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
+          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -692,39 +692,39 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>16883</t>
+          <t>17362</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
+          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -749,34 +749,34 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>16882</t>
+          <t>16883</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
+          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -818,27 +818,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>16881</t>
+          <t>16882</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
+          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -875,32 +875,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>16314</t>
+          <t>16881</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
+          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -910,44 +910,44 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>16313</t>
+          <t>16314</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>370</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
+          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -989,22 +989,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>16312</t>
+          <t>16313</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>371</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
+          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1046,22 +1046,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>16311</t>
+          <t>16312</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>372</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
+          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1103,32 +1103,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>14451</t>
+          <t>16311</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>373</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
+          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1148,39 +1148,39 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>14433</t>
+          <t>14451</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>369</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1205,34 +1205,34 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>14422</t>
+          <t>14433</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>366</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1252,49 +1252,49 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14422</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
+          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1331,32 +1331,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>11392</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
+          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1366,44 +1366,44 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>11391</t>
+          <t>11392</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>367</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
+          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1445,27 +1445,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>11221</t>
+          <t>11391</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>368</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
+          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1480,54 +1480,54 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>11221</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
+          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1547,44 +1547,44 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>9501</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>인프라표준화팀</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1604,44 +1604,44 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>9381</t>
+          <t>9501</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
+          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>인프라표준화팀</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1661,39 +1661,39 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>9271</t>
+          <t>9381</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
+          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>법무감사담당관</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1703,116 +1703,116 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>303</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6541</t>
+          <t>9271</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>365</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
+          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>법무감사담당관</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5491</t>
+          <t>6541</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
+          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1822,49 +1822,49 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>364</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
+          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>장석인</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1879,49 +1879,49 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
+          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>장석인</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1958,27 +1958,27 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
+          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1993,54 +1993,54 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>5391</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>363</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
+          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2050,54 +2050,54 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
+          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2107,49 +2107,49 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>362</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
+          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2164,49 +2164,49 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
+          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2243,32 +2243,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
+          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2288,39 +2288,39 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
+          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2345,39 +2345,39 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2402,44 +2402,44 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>561</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
+          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2459,19 +2459,19 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>281</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2481,17 +2481,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
+          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2516,44 +2516,44 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
+          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>98</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2585,27 +2585,27 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
+          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>924</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2642,27 +2642,27 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
+          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2699,32 +2699,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2734,49 +2734,49 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>743</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>361</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2791,54 +2791,54 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2848,49 +2848,49 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>360</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2905,49 +2905,49 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
+          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2984,27 +2984,27 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>AI 범죄 대응 범부처 협의체 출범</t>
+          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3041,32 +3041,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
+          <t>AI 범죄 대응 범부처 협의체 출범</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3076,49 +3076,49 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>359</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3133,49 +3133,49 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
+          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>2754</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3212,32 +3212,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
+          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3247,54 +3247,54 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>7681</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>358</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
+          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>7681</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3326,32 +3326,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>357</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
+          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3383,32 +3383,32 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>356</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>11169</t>
+          <t>9023</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3440,12 +3440,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>352</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3455,17 +3455,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>13472</t>
+          <t>11169</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3497,27 +3497,27 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>354</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>13472</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3554,55 +3554,112 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>신기술개인정보과</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>9724</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>353</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>「개인정보 처리 방법에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12127</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>전략기획팀</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
         <is>
           <t>11519</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>공지사항</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>

--- a/docs/snapshot/downloads/pipc.xlsx
+++ b/docs/snapshot/downloads/pipc.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K57"/>
+  <dimension ref="A1:K58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,32 +476,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>22661</t>
+          <t>28361</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>개인정보위, ‘㈜KT의개인정보 유출사고’ 제재처분 의결</t>
+          <t>인공지능(AI) 시대 개인정보 제도 혁신, 국민과 함께 설계한다</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12349</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12361</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -511,7 +511,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -521,44 +521,44 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30:27.268351+09:00</t>
+          <t>2026-08-06 10:00:26.758706+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30:27.268351+09:00</t>
+          <t>2026-08-06 10:00:26.758706+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>22391</t>
+          <t>22661</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>개인정보 영향평가기관 지정갱신 공고</t>
+          <t>개인정보위, ‘㈜KT의개인정보 유출사고’ 제재처분 의결</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12349</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -568,29 +568,29 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>22351</t>
+          <t>22391</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -635,44 +635,44 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>17701</t>
+          <t>22351</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>374</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
+          <t>개인정보 영향평가기관 지정갱신 공고</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -682,54 +682,54 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>17362</t>
+          <t>17701</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
+          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -749,39 +749,39 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>16883</t>
+          <t>17362</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
+          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -806,34 +806,34 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>16882</t>
+          <t>16883</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
+          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -875,27 +875,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>16881</t>
+          <t>16882</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
+          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -932,32 +932,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>16314</t>
+          <t>16881</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
+          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -967,44 +967,44 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>16313</t>
+          <t>16314</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>370</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
+          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1046,22 +1046,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>16312</t>
+          <t>16313</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>371</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
+          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1103,22 +1103,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>16311</t>
+          <t>16312</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>372</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
+          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1160,32 +1160,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>14451</t>
+          <t>16311</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>373</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
+          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1205,39 +1205,39 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>14433</t>
+          <t>14451</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>369</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1262,34 +1262,34 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>14422</t>
+          <t>14433</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>366</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1309,49 +1309,49 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14422</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
+          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1388,32 +1388,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>11392</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
+          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1423,44 +1423,44 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>11391</t>
+          <t>11392</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>367</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
+          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1502,27 +1502,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>11221</t>
+          <t>11391</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>368</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
+          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1537,54 +1537,54 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>11221</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
+          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1604,44 +1604,44 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>9501</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>인프라표준화팀</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1661,44 +1661,44 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>9381</t>
+          <t>9501</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
+          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>인프라표준화팀</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1718,39 +1718,39 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>9271</t>
+          <t>9381</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
+          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>법무감사담당관</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1760,116 +1760,116 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>303</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>6541</t>
+          <t>9271</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>365</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
+          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>법무감사담당관</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5491</t>
+          <t>6541</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
+          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1879,49 +1879,49 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>364</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
+          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>장석인</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1936,49 +1936,49 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
+          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>장석인</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2015,27 +2015,27 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
+          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2050,54 +2050,54 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>5391</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>363</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
+          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2107,54 +2107,54 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
+          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2164,49 +2164,49 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>362</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
+          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2221,49 +2221,49 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
+          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2300,32 +2300,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
+          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2345,39 +2345,39 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
+          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2402,39 +2402,39 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2459,44 +2459,44 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>561</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
+          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2516,19 +2516,19 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>281</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2538,17 +2538,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
+          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2573,44 +2573,44 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
+          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>98</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2642,27 +2642,27 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
+          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>924</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2699,27 +2699,27 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
+          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2756,32 +2756,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2791,49 +2791,49 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>743</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>361</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2848,54 +2848,54 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2905,49 +2905,49 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>360</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2962,49 +2962,49 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
+          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3041,27 +3041,27 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AI 범죄 대응 범부처 협의체 출범</t>
+          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3098,32 +3098,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
+          <t>AI 범죄 대응 범부처 협의체 출범</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3133,49 +3133,49 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>359</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3190,49 +3190,49 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
+          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>2754</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3269,32 +3269,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
+          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3304,54 +3304,54 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>7681</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>358</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
+          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>7681</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3383,32 +3383,32 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>357</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
+          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3440,32 +3440,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>356</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>11169</t>
+          <t>9023</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3497,12 +3497,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>352</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3512,17 +3512,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>13472</t>
+          <t>11169</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3554,27 +3554,27 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>354</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>13472</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3611,55 +3611,112 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>신기술개인정보과</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>9724</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>353</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>「개인정보 처리 방법에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12127</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>전략기획팀</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
         <is>
           <t>11519</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>공지사항</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="K58" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>

--- a/docs/snapshot/downloads/pipc.xlsx
+++ b/docs/snapshot/downloads/pipc.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K58"/>
+  <dimension ref="A1:K59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,27 +476,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>28361</t>
+          <t>28831</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>375</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>인공지능(AI) 시대 개인정보 제도 혁신, 국민과 함께 설계한다</t>
+          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12361</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -506,59 +506,59 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-08-06 10:00:26.758706+09:00</t>
+          <t>2026-08-06 15:46:06.392884+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-06 10:00:26.758706+09:00</t>
+          <t>2026-08-06 15:46:06.392884+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>22661</t>
+          <t>28361</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>개인정보위, ‘㈜KT의개인정보 유출사고’ 제재처분 의결</t>
+          <t>인공지능(AI) 시대 개인정보 제도 혁신, 국민과 함께 설계한다</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12349</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12361</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -578,44 +578,44 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30:27.268351+09:00</t>
+          <t>2026-08-06 10:00:26.758706+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30:27.268351+09:00</t>
+          <t>2026-08-06 10:00:26.758706+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>22391</t>
+          <t>22661</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>개인정보 영향평가기관 지정갱신 공고</t>
+          <t>개인정보위, ‘㈜KT의개인정보 유출사고’ 제재처분 의결</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12349</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -625,29 +625,29 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>22351</t>
+          <t>22391</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -692,44 +692,44 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>17701</t>
+          <t>22351</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>374</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
+          <t>개인정보 영향평가기관 지정갱신 공고</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -739,54 +739,54 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>17362</t>
+          <t>17701</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
+          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -806,39 +806,39 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>16883</t>
+          <t>17362</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
+          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -863,34 +863,34 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>16882</t>
+          <t>16883</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
+          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -932,27 +932,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>16881</t>
+          <t>16882</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
+          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -989,32 +989,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>16314</t>
+          <t>16881</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
+          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1024,44 +1024,44 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>16313</t>
+          <t>16314</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>370</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
+          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1103,22 +1103,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>16312</t>
+          <t>16313</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>371</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
+          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1160,22 +1160,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>16311</t>
+          <t>16312</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>372</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
+          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1217,32 +1217,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>14451</t>
+          <t>16311</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>373</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
+          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1262,39 +1262,39 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>14433</t>
+          <t>14451</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>369</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1319,34 +1319,34 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>14422</t>
+          <t>14433</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>366</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1366,49 +1366,49 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14422</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
+          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1445,32 +1445,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>11392</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
+          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1480,44 +1480,44 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>11391</t>
+          <t>11392</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>367</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
+          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1559,27 +1559,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>11221</t>
+          <t>11391</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>368</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
+          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1594,54 +1594,54 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>11221</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
+          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1661,44 +1661,44 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>9501</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>인프라표준화팀</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1718,44 +1718,44 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>9381</t>
+          <t>9501</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
+          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>인프라표준화팀</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1775,39 +1775,39 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>9271</t>
+          <t>9381</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
+          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>법무감사담당관</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1817,116 +1817,116 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>303</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>6541</t>
+          <t>9271</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>365</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
+          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>법무감사담당관</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5491</t>
+          <t>6541</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
+          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1936,49 +1936,49 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>364</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
+          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>장석인</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1993,49 +1993,49 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
+          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>장석인</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2072,27 +2072,27 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
+          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2107,54 +2107,54 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>5391</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>363</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
+          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2164,54 +2164,54 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
+          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2221,49 +2221,49 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>362</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
+          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2278,49 +2278,49 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
+          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2357,32 +2357,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
+          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2402,39 +2402,39 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
+          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2459,39 +2459,39 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2516,44 +2516,44 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>561</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
+          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2573,19 +2573,19 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>281</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2595,17 +2595,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
+          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2630,44 +2630,44 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
+          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>98</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2699,27 +2699,27 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
+          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>924</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2756,27 +2756,27 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
+          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2813,32 +2813,32 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2848,49 +2848,49 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>743</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>361</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2905,54 +2905,54 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2962,49 +2962,49 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>360</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3019,49 +3019,49 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
+          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3098,27 +3098,27 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>AI 범죄 대응 범부처 협의체 출범</t>
+          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3155,32 +3155,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
+          <t>AI 범죄 대응 범부처 협의체 출범</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3190,49 +3190,49 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>359</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3247,49 +3247,49 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
+          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>2754</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3326,32 +3326,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
+          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3361,54 +3361,54 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>7681</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>358</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
+          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>7681</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3440,32 +3440,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>357</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
+          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3497,32 +3497,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>356</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>11169</t>
+          <t>9023</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3554,12 +3554,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>352</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3569,17 +3569,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>13472</t>
+          <t>11169</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3611,27 +3611,27 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>354</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>13472</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3668,55 +3668,112 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>신기술개인정보과</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>9724</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>353</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>「개인정보 처리 방법에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12127</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>전략기획팀</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
         <is>
           <t>11519</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>공지사항</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="K59" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>

--- a/docs/snapshot/downloads/pipc.xlsx
+++ b/docs/snapshot/downloads/pipc.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K59"/>
+  <dimension ref="A1:K61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,42 +476,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>28831</t>
+          <t>32571</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>376</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제3자 제공사항 알림</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -521,44 +521,44 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-08-06 15:46:06.392884+09:00</t>
+          <t>2026-08-11 11:16:08.723253+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-06 15:46:06.392884+09:00</t>
+          <t>2026-08-11 11:16:08.723253+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>28361</t>
+          <t>32541</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>인공지능(AI) 시대 개인정보 제도 혁신, 국민과 함께 설계한다</t>
+          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12361</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -578,101 +578,101 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-06 10:00:26.758706+09:00</t>
+          <t>2026-08-11 11:00:26.976860+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-06 10:00:26.758706+09:00</t>
+          <t>2026-08-11 11:00:26.976860+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>22661</t>
+          <t>28831</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>375</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>개인정보위, ‘㈜KT의개인정보 유출사고’ 제재처분 의결</t>
+          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12349</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30:27.268351+09:00</t>
+          <t>2026-08-06 15:46:06.392884+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30:27.268351+09:00</t>
+          <t>2026-08-06 15:46:06.392884+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>22391</t>
+          <t>28361</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>개인정보 영향평가기관 지정갱신 공고</t>
+          <t>인공지능(AI) 시대 개인정보 제도 혁신, 국민과 함께 설계한다</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12361</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -682,54 +682,54 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-08-06 10:00:26.758706+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-08-06 10:00:26.758706+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>22351</t>
+          <t>22661</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>개인정보 영향평가기관 지정갱신 공고</t>
+          <t>개인정보위, ‘㈜KT의개인정보 유출사고’ 제재처분 의결</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12349</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -739,54 +739,54 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>17701</t>
+          <t>22391</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>374</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
+          <t>개인정보 영향평가기관 지정갱신 공고</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -796,54 +796,54 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>17362</t>
+          <t>22351</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>374</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
+          <t>개인정보 영향평가기관 지정갱신 공고</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -853,54 +853,54 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>16883</t>
+          <t>17701</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
+          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -920,19 +920,19 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>16882</t>
+          <t>17362</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -942,17 +942,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
+          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -977,39 +977,39 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>16881</t>
+          <t>16883</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
+          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1046,32 +1046,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>16314</t>
+          <t>16882</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
+          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1081,54 +1081,54 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>16313</t>
+          <t>16881</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
+          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1138,44 +1138,44 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>16312</t>
+          <t>16314</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>370</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
+          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1217,22 +1217,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>16311</t>
+          <t>16313</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>371</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
+          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1274,32 +1274,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>14451</t>
+          <t>16312</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>372</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
+          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1319,44 +1319,44 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>14433</t>
+          <t>16311</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>373</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1376,39 +1376,39 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>14422</t>
+          <t>14451</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>369</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1423,49 +1423,49 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14433</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>366</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1480,54 +1480,54 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>11392</t>
+          <t>14422</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
+          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1537,54 +1537,54 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>11391</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
+          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1594,49 +1594,49 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>11221</t>
+          <t>11392</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>367</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
+          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1651,54 +1651,54 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>11391</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>368</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
+          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1708,54 +1708,54 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>9501</t>
+          <t>11221</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
+          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>인프라표준화팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1775,19 +1775,19 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>9381</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1797,22 +1797,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1832,101 +1832,101 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>9271</t>
+          <t>9501</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
+          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>법무감사담당관</t>
+          <t>인프라표준화팀</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>6541</t>
+          <t>9381</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
+          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>303</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1946,54 +1946,54 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5491</t>
+          <t>9271</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>365</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
+          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>법무감사담당관</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2003,44 +2003,44 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>6541</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
+          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>장석인</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2060,34 +2060,34 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>364</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
+          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2107,49 +2107,49 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
+          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>장석인</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2164,54 +2164,54 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
+          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2231,44 +2231,44 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>5391</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>363</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
+          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2288,44 +2288,44 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
+          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2345,39 +2345,39 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>362</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
+          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2392,54 +2392,54 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
+          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2459,44 +2459,44 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
+          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2516,39 +2516,39 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
+          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2573,44 +2573,44 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2630,44 +2630,44 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>561</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
+          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2687,44 +2687,44 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>281</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
+          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2744,44 +2744,44 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
+          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>98</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2813,27 +2813,27 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
+          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>924</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2870,32 +2870,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
+          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2905,44 +2905,44 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>743</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2984,32 +2984,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>361</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3041,32 +3041,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3098,22 +3098,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>360</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3133,49 +3133,49 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AI 범죄 대응 범부처 협의체 출범</t>
+          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3212,32 +3212,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
+          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3247,54 +3247,54 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
+          <t>AI 범죄 대응 범부처 협의체 출범</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3326,22 +3326,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>359</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3361,54 +3361,54 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
+          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3418,54 +3418,54 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>7681</t>
+          <t>2754</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
+          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3475,44 +3475,44 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>358</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
+          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>7681</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3554,32 +3554,32 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>357</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>11169</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3611,32 +3611,32 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>356</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>13472</t>
+          <t>9023</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3668,32 +3668,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>352</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>11169</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3725,55 +3725,169 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>354</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>조사총괄과</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>13472</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>신기술개인정보과</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>9724</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>353</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>「개인정보 처리 방법에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12127</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>전략기획팀</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
         <is>
           <t>11519</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>공지사항</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="K61" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>

--- a/docs/snapshot/downloads/pipc.xlsx
+++ b/docs/snapshot/downloads/pipc.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K61"/>
+  <dimension ref="A1:K62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,32 +476,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>32571</t>
+          <t>34071</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>377</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
+          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -511,7 +511,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -521,39 +521,39 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-08-11 11:16:08.723253+09:00</t>
+          <t>2026-08-13 09:31:08.209725+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-11 11:16:08.723253+09:00</t>
+          <t>2026-08-13 09:31:08.209725+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>32541</t>
+          <t>32571</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>376</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -568,106 +568,106 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-11 11:00:26.976860+09:00</t>
+          <t>2026-08-11 11:16:08.723253+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-11 11:00:26.976860+09:00</t>
+          <t>2026-08-11 11:16:08.723253+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>28831</t>
+          <t>32541</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제3자 제공사항 알림</t>
+          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-08-06 15:46:06.392884+09:00</t>
+          <t>2026-08-11 11:00:26.976860+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-08-06 15:46:06.392884+09:00</t>
+          <t>2026-08-11 11:00:26.976860+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>28361</t>
+          <t>28831</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>375</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>인공지능(AI) 시대 개인정보 제도 혁신, 국민과 함께 설계한다</t>
+          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12361</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -677,59 +677,59 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-08-06 10:00:26.758706+09:00</t>
+          <t>2026-08-06 15:46:06.392884+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-08-06 10:00:26.758706+09:00</t>
+          <t>2026-08-06 15:46:06.392884+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>22661</t>
+          <t>28361</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>개인정보위, ‘㈜KT의개인정보 유출사고’ 제재처분 의결</t>
+          <t>인공지능(AI) 시대 개인정보 제도 혁신, 국민과 함께 설계한다</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12349</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12361</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -749,44 +749,44 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30:27.268351+09:00</t>
+          <t>2026-08-06 10:00:26.758706+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30:27.268351+09:00</t>
+          <t>2026-08-06 10:00:26.758706+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>22391</t>
+          <t>22661</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>개인정보 영향평가기관 지정갱신 공고</t>
+          <t>개인정보위, ‘㈜KT의개인정보 유출사고’ 제재처분 의결</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12349</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -796,29 +796,29 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>22351</t>
+          <t>22391</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -833,7 +833,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -863,44 +863,44 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>17701</t>
+          <t>22351</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>374</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
+          <t>개인정보 영향평가기관 지정갱신 공고</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -910,54 +910,54 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>17362</t>
+          <t>17701</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
+          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -977,39 +977,39 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>16883</t>
+          <t>17362</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
+          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1034,34 +1034,34 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>16882</t>
+          <t>16883</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
+          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1103,27 +1103,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>16881</t>
+          <t>16882</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
+          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1160,32 +1160,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>16314</t>
+          <t>16881</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
+          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1195,44 +1195,44 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>16313</t>
+          <t>16314</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>370</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
+          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1274,22 +1274,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>16312</t>
+          <t>16313</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>371</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
+          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1331,22 +1331,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>16311</t>
+          <t>16312</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>372</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
+          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1388,32 +1388,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>14451</t>
+          <t>16311</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>373</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
+          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1433,39 +1433,39 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>14433</t>
+          <t>14451</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>369</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1490,34 +1490,34 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>14422</t>
+          <t>14433</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>366</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1537,49 +1537,49 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14422</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
+          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1616,32 +1616,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>11392</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
+          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1651,44 +1651,44 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>11391</t>
+          <t>11392</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>367</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
+          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1730,27 +1730,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>11221</t>
+          <t>11391</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>368</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
+          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1765,54 +1765,54 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>11221</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
+          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1832,44 +1832,44 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>9501</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>인프라표준화팀</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1889,44 +1889,44 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>9381</t>
+          <t>9501</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
+          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>인프라표준화팀</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1946,39 +1946,39 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>9271</t>
+          <t>9381</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
+          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>법무감사담당관</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1988,116 +1988,116 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>303</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>6541</t>
+          <t>9271</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>365</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
+          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>법무감사담당관</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>5491</t>
+          <t>6541</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
+          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2107,49 +2107,49 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>364</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
+          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>장석인</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2164,49 +2164,49 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
+          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>장석인</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2243,27 +2243,27 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
+          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2278,54 +2278,54 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>5391</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>363</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
+          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2335,54 +2335,54 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
+          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2392,49 +2392,49 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>362</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
+          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2449,49 +2449,49 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
+          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2528,32 +2528,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
+          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2573,39 +2573,39 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
+          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2630,39 +2630,39 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2687,44 +2687,44 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>561</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
+          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2744,19 +2744,19 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>281</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2766,17 +2766,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
+          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2801,44 +2801,44 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
+          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>98</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2870,27 +2870,27 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
+          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>924</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2927,27 +2927,27 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
+          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2984,32 +2984,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3019,49 +3019,49 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>743</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>361</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3076,54 +3076,54 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3133,49 +3133,49 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>360</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3190,49 +3190,49 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
+          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3269,27 +3269,27 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AI 범죄 대응 범부처 협의체 출범</t>
+          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3326,32 +3326,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
+          <t>AI 범죄 대응 범부처 협의체 출범</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3361,49 +3361,49 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>359</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3418,49 +3418,49 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
+          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>2754</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3497,32 +3497,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
+          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3532,54 +3532,54 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>7681</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>358</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
+          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>7681</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3611,32 +3611,32 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>357</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
+          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3668,32 +3668,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>356</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>11169</t>
+          <t>9023</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3725,12 +3725,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>352</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3740,17 +3740,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>13472</t>
+          <t>11169</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3782,27 +3782,27 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>354</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>13472</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3839,55 +3839,112 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>신기술개인정보과</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>9724</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>353</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>「개인정보 처리 방법에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12127</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>전략기획팀</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
         <is>
           <t>11519</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t>공지사항</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="K62" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>

--- a/docs/snapshot/downloads/pipc.xlsx
+++ b/docs/snapshot/downloads/pipc.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K62"/>
+  <dimension ref="A1:K63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,27 +476,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>34071</t>
+          <t>34691</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>378</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
+          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12375</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -506,12 +506,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -521,44 +521,44 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:08.209725+09:00</t>
+          <t>2026-08-13 17:16:11.373869+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:08.209725+09:00</t>
+          <t>2026-08-13 17:16:11.373869+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>32571</t>
+          <t>34071</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>377</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
+          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -578,39 +578,39 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-11 11:16:08.723253+09:00</t>
+          <t>2026-08-13 09:31:08.209725+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-11 11:16:08.723253+09:00</t>
+          <t>2026-08-13 09:31:08.209725+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>32541</t>
+          <t>32571</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>376</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -625,106 +625,106 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-08-11 11:00:26.976860+09:00</t>
+          <t>2026-08-11 11:16:08.723253+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-08-11 11:00:26.976860+09:00</t>
+          <t>2026-08-11 11:16:08.723253+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>28831</t>
+          <t>32541</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제3자 제공사항 알림</t>
+          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-08-06 15:46:06.392884+09:00</t>
+          <t>2026-08-11 11:00:26.976860+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-08-06 15:46:06.392884+09:00</t>
+          <t>2026-08-11 11:00:26.976860+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>28361</t>
+          <t>28831</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>375</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>인공지능(AI) 시대 개인정보 제도 혁신, 국민과 함께 설계한다</t>
+          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12361</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -734,59 +734,59 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-08-06 10:00:26.758706+09:00</t>
+          <t>2026-08-06 15:46:06.392884+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-08-06 10:00:26.758706+09:00</t>
+          <t>2026-08-06 15:46:06.392884+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>22661</t>
+          <t>28361</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>개인정보위, ‘㈜KT의개인정보 유출사고’ 제재처분 의결</t>
+          <t>인공지능(AI) 시대 개인정보 제도 혁신, 국민과 함께 설계한다</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12349</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12361</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -806,44 +806,44 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30:27.268351+09:00</t>
+          <t>2026-08-06 10:00:26.758706+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30:27.268351+09:00</t>
+          <t>2026-08-06 10:00:26.758706+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>22391</t>
+          <t>22661</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>개인정보 영향평가기관 지정갱신 공고</t>
+          <t>개인정보위, ‘㈜KT의개인정보 유출사고’ 제재처분 의결</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12349</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -853,29 +853,29 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>22351</t>
+          <t>22391</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -920,44 +920,44 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>17701</t>
+          <t>22351</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>374</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
+          <t>개인정보 영향평가기관 지정갱신 공고</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -967,54 +967,54 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>17362</t>
+          <t>17701</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
+          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1034,39 +1034,39 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>16883</t>
+          <t>17362</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
+          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1091,34 +1091,34 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>16882</t>
+          <t>16883</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
+          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1160,27 +1160,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>16881</t>
+          <t>16882</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
+          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1217,32 +1217,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>16314</t>
+          <t>16881</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
+          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1252,44 +1252,44 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>16313</t>
+          <t>16314</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>370</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
+          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1331,22 +1331,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>16312</t>
+          <t>16313</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>371</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
+          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1388,22 +1388,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>16311</t>
+          <t>16312</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>372</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
+          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1445,32 +1445,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>14451</t>
+          <t>16311</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>373</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
+          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1490,39 +1490,39 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>14433</t>
+          <t>14451</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>369</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1547,34 +1547,34 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>14422</t>
+          <t>14433</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>366</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1594,49 +1594,49 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14422</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
+          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1673,32 +1673,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>11392</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
+          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1708,44 +1708,44 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>11391</t>
+          <t>11392</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>367</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
+          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1787,27 +1787,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>11221</t>
+          <t>11391</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>368</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
+          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1822,54 +1822,54 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>11221</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
+          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1889,44 +1889,44 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>9501</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>인프라표준화팀</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1946,44 +1946,44 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>9381</t>
+          <t>9501</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
+          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>인프라표준화팀</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2003,39 +2003,39 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>9271</t>
+          <t>9381</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
+          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>법무감사담당관</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2045,116 +2045,116 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>303</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>6541</t>
+          <t>9271</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>365</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
+          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>법무감사담당관</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5491</t>
+          <t>6541</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
+          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2164,49 +2164,49 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>364</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
+          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>장석인</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2221,49 +2221,49 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
+          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>장석인</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2300,27 +2300,27 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
+          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2335,54 +2335,54 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>5391</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>363</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
+          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2392,54 +2392,54 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
+          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2449,49 +2449,49 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>362</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
+          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2506,49 +2506,49 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
+          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2585,32 +2585,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
+          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2630,39 +2630,39 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
+          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2687,39 +2687,39 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2744,44 +2744,44 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>561</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
+          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2801,19 +2801,19 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>281</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2823,17 +2823,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
+          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2858,44 +2858,44 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
+          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>98</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2927,27 +2927,27 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
+          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>924</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2984,27 +2984,27 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
+          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3041,32 +3041,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3076,49 +3076,49 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>743</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>361</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3133,54 +3133,54 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3190,49 +3190,49 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>360</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3247,49 +3247,49 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
+          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3326,27 +3326,27 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>AI 범죄 대응 범부처 협의체 출범</t>
+          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3383,32 +3383,32 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
+          <t>AI 범죄 대응 범부처 협의체 출범</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3418,49 +3418,49 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>359</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3475,49 +3475,49 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
+          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>2754</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3554,32 +3554,32 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
+          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3589,54 +3589,54 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>7681</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>358</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
+          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>7681</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3668,32 +3668,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>357</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
+          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3725,32 +3725,32 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>356</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>11169</t>
+          <t>9023</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3782,12 +3782,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>352</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3797,17 +3797,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>13472</t>
+          <t>11169</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3839,27 +3839,27 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>354</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>13472</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3896,55 +3896,112 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>신기술개인정보과</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>9724</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>353</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>「개인정보 처리 방법에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12127</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>전략기획팀</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
         <is>
           <t>11519</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>공지사항</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="K63" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>

--- a/docs/snapshot/downloads/pipc.xlsx
+++ b/docs/snapshot/downloads/pipc.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K63"/>
+  <dimension ref="A1:K64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,27 +476,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>34691</t>
+          <t>34711</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>379</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
+          <t>「국경 간 개인정보 보호 규칙 인증제도의 운영에 관한 지침」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12375</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -506,12 +506,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -521,39 +521,39 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-08-13 17:16:11.373869+09:00</t>
+          <t>2026-08-13 17:31:09.311303+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-13 17:16:11.373869+09:00</t>
+          <t>2026-08-13 17:31:09.311303+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>34071</t>
+          <t>34691</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>378</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
+          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12375</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -563,12 +563,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -578,44 +578,44 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:08.209725+09:00</t>
+          <t>2026-08-13 17:16:11.373869+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:08.209725+09:00</t>
+          <t>2026-08-13 17:16:11.373869+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>32571</t>
+          <t>34071</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>377</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
+          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -635,39 +635,39 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-08-11 11:16:08.723253+09:00</t>
+          <t>2026-08-13 09:31:08.209725+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-08-11 11:16:08.723253+09:00</t>
+          <t>2026-08-13 09:31:08.209725+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>32541</t>
+          <t>32571</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>376</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -682,106 +682,106 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-08-11 11:00:26.976860+09:00</t>
+          <t>2026-08-11 11:16:08.723253+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-08-11 11:00:26.976860+09:00</t>
+          <t>2026-08-11 11:16:08.723253+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>28831</t>
+          <t>32541</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제3자 제공사항 알림</t>
+          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-08-06 15:46:06.392884+09:00</t>
+          <t>2026-08-11 11:00:26.976860+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-08-06 15:46:06.392884+09:00</t>
+          <t>2026-08-11 11:00:26.976860+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>28361</t>
+          <t>28831</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>375</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>인공지능(AI) 시대 개인정보 제도 혁신, 국민과 함께 설계한다</t>
+          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12361</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -791,59 +791,59 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-08-06 10:00:26.758706+09:00</t>
+          <t>2026-08-06 15:46:06.392884+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-08-06 10:00:26.758706+09:00</t>
+          <t>2026-08-06 15:46:06.392884+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>22661</t>
+          <t>28361</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>개인정보위, ‘㈜KT의개인정보 유출사고’ 제재처분 의결</t>
+          <t>인공지능(AI) 시대 개인정보 제도 혁신, 국민과 함께 설계한다</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12349</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12361</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -863,44 +863,44 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30:27.268351+09:00</t>
+          <t>2026-08-06 10:00:26.758706+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30:27.268351+09:00</t>
+          <t>2026-08-06 10:00:26.758706+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>22391</t>
+          <t>22661</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>개인정보 영향평가기관 지정갱신 공고</t>
+          <t>개인정보위, ‘㈜KT의개인정보 유출사고’ 제재처분 의결</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12349</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -910,29 +910,29 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>22351</t>
+          <t>22391</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -977,44 +977,44 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>17701</t>
+          <t>22351</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>374</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
+          <t>개인정보 영향평가기관 지정갱신 공고</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1024,54 +1024,54 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>17362</t>
+          <t>17701</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
+          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1091,39 +1091,39 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>16883</t>
+          <t>17362</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
+          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1148,34 +1148,34 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>16882</t>
+          <t>16883</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
+          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1217,27 +1217,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>16881</t>
+          <t>16882</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
+          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1274,32 +1274,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>16314</t>
+          <t>16881</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
+          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1309,44 +1309,44 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>16313</t>
+          <t>16314</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>370</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
+          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1388,22 +1388,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>16312</t>
+          <t>16313</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>371</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
+          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1445,22 +1445,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>16311</t>
+          <t>16312</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>372</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
+          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1502,32 +1502,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>14451</t>
+          <t>16311</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>373</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
+          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1547,39 +1547,39 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>14433</t>
+          <t>14451</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>369</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1604,34 +1604,34 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>14422</t>
+          <t>14433</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>366</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1651,49 +1651,49 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14422</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
+          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1730,32 +1730,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>11392</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
+          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1765,44 +1765,44 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>11391</t>
+          <t>11392</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>367</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
+          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1844,27 +1844,27 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>11221</t>
+          <t>11391</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>368</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
+          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1879,54 +1879,54 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>11221</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
+          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1946,44 +1946,44 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>9501</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>인프라표준화팀</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2003,44 +2003,44 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>9381</t>
+          <t>9501</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
+          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>인프라표준화팀</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2060,39 +2060,39 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>9271</t>
+          <t>9381</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
+          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>법무감사담당관</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2102,116 +2102,116 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>303</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>6541</t>
+          <t>9271</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>365</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
+          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>법무감사담당관</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5491</t>
+          <t>6541</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
+          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2221,49 +2221,49 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>364</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
+          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>장석인</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2278,49 +2278,49 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
+          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>장석인</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2357,27 +2357,27 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
+          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2392,54 +2392,54 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>5391</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>363</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
+          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2449,54 +2449,54 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
+          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2506,49 +2506,49 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>362</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
+          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2563,49 +2563,49 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
+          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2642,32 +2642,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
+          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2687,39 +2687,39 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
+          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2744,39 +2744,39 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2801,44 +2801,44 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>561</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
+          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2858,19 +2858,19 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>281</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2880,17 +2880,17 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
+          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2915,44 +2915,44 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
+          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>98</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2984,27 +2984,27 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
+          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>924</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3041,27 +3041,27 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
+          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3098,32 +3098,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3133,49 +3133,49 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>743</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>361</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3190,54 +3190,54 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3247,49 +3247,49 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>360</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3304,49 +3304,49 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
+          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3383,27 +3383,27 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>AI 범죄 대응 범부처 협의체 출범</t>
+          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3440,32 +3440,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
+          <t>AI 범죄 대응 범부처 협의체 출범</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3475,49 +3475,49 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>359</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3532,49 +3532,49 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
+          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>2754</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3611,32 +3611,32 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
+          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3646,54 +3646,54 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>7681</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>358</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
+          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>7681</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3725,32 +3725,32 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>357</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
+          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3782,32 +3782,32 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>356</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>11169</t>
+          <t>9023</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3839,12 +3839,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>352</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3854,17 +3854,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>13472</t>
+          <t>11169</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3896,27 +3896,27 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>354</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>13472</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3953,55 +3953,112 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>신기술개인정보과</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>9724</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>353</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>「개인정보 처리 방법에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12127</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>전략기획팀</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
         <is>
           <t>11519</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t>공지사항</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="K64" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>

--- a/docs/snapshot/downloads/pipc.xlsx
+++ b/docs/snapshot/downloads/pipc.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K64"/>
+  <dimension ref="A1:K65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>34711</t>
+          <t>35591</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -486,22 +486,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>「국경 간 개인정보 보호 규칙 인증제도의 운영에 관한 지침」 일부개정안 행정예고</t>
+          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -511,7 +511,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -521,39 +521,39 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-08-13 17:31:09.311303+09:00</t>
+          <t>2026-08-14 18:16:08.177242+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-13 17:31:09.311303+09:00</t>
+          <t>2026-08-14 18:16:08.177242+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>34691</t>
+          <t>34711</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>379</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
+          <t>「국경 간 개인정보 보호 규칙 인증제도의 운영에 관한 지침」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12375</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -563,12 +563,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -578,39 +578,39 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-13 17:16:11.373869+09:00</t>
+          <t>2026-08-13 17:31:09.311303+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-13 17:16:11.373869+09:00</t>
+          <t>2026-08-13 17:31:09.311303+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>34071</t>
+          <t>34691</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>378</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
+          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12375</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -620,12 +620,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -635,44 +635,44 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:08.209725+09:00</t>
+          <t>2026-08-13 17:16:11.373869+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:08.209725+09:00</t>
+          <t>2026-08-13 17:16:11.373869+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>32571</t>
+          <t>34071</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>377</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
+          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -692,39 +692,39 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-08-11 11:16:08.723253+09:00</t>
+          <t>2026-08-13 09:31:08.209725+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-08-11 11:16:08.723253+09:00</t>
+          <t>2026-08-13 09:31:08.209725+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>32541</t>
+          <t>32571</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>376</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -739,106 +739,106 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-08-11 11:00:26.976860+09:00</t>
+          <t>2026-08-11 11:16:08.723253+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-08-11 11:00:26.976860+09:00</t>
+          <t>2026-08-11 11:16:08.723253+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>28831</t>
+          <t>32541</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제3자 제공사항 알림</t>
+          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-08-06 15:46:06.392884+09:00</t>
+          <t>2026-08-11 11:00:26.976860+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-08-06 15:46:06.392884+09:00</t>
+          <t>2026-08-11 11:00:26.976860+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>28361</t>
+          <t>28831</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>375</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>인공지능(AI) 시대 개인정보 제도 혁신, 국민과 함께 설계한다</t>
+          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12361</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -848,59 +848,59 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-08-06 10:00:26.758706+09:00</t>
+          <t>2026-08-06 15:46:06.392884+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-08-06 10:00:26.758706+09:00</t>
+          <t>2026-08-06 15:46:06.392884+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>22661</t>
+          <t>28361</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>개인정보위, ‘㈜KT의개인정보 유출사고’ 제재처분 의결</t>
+          <t>인공지능(AI) 시대 개인정보 제도 혁신, 국민과 함께 설계한다</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12349</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12361</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -920,44 +920,44 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30:27.268351+09:00</t>
+          <t>2026-08-06 10:00:26.758706+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30:27.268351+09:00</t>
+          <t>2026-08-06 10:00:26.758706+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>22391</t>
+          <t>22661</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>개인정보 영향평가기관 지정갱신 공고</t>
+          <t>개인정보위, ‘㈜KT의개인정보 유출사고’ 제재처분 의결</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12349</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -967,29 +967,29 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>22351</t>
+          <t>22391</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1034,44 +1034,44 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>17701</t>
+          <t>22351</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>374</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
+          <t>개인정보 영향평가기관 지정갱신 공고</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1081,54 +1081,54 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>17362</t>
+          <t>17701</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
+          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1148,39 +1148,39 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>16883</t>
+          <t>17362</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
+          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1205,34 +1205,34 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>16882</t>
+          <t>16883</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
+          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1274,27 +1274,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>16881</t>
+          <t>16882</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
+          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1331,32 +1331,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>16314</t>
+          <t>16881</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
+          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1366,44 +1366,44 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>16313</t>
+          <t>16314</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>370</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
+          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1445,22 +1445,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>16312</t>
+          <t>16313</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>371</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
+          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1502,22 +1502,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>16311</t>
+          <t>16312</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>372</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
+          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1559,32 +1559,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>14451</t>
+          <t>16311</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>373</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
+          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1604,39 +1604,39 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>14433</t>
+          <t>14451</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>369</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1661,34 +1661,34 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>14422</t>
+          <t>14433</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>366</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1708,49 +1708,49 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14422</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
+          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1787,32 +1787,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>11392</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
+          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1822,44 +1822,44 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>11391</t>
+          <t>11392</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>367</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
+          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1901,27 +1901,27 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>11221</t>
+          <t>11391</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>368</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
+          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1936,54 +1936,54 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>11221</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
+          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2003,44 +2003,44 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>9501</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>인프라표준화팀</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2060,44 +2060,44 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>9381</t>
+          <t>9501</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
+          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>인프라표준화팀</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2117,39 +2117,39 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>9271</t>
+          <t>9381</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
+          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>법무감사담당관</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2159,116 +2159,116 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>303</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>6541</t>
+          <t>9271</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>365</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
+          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>법무감사담당관</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5491</t>
+          <t>6541</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
+          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2278,49 +2278,49 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>364</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
+          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>장석인</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2335,49 +2335,49 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
+          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>장석인</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2414,27 +2414,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
+          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2449,54 +2449,54 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>5391</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>363</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
+          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2506,54 +2506,54 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
+          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2563,49 +2563,49 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>362</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
+          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2620,49 +2620,49 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
+          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2699,32 +2699,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
+          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2744,39 +2744,39 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
+          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2801,39 +2801,39 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2858,44 +2858,44 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>561</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
+          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2915,19 +2915,19 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>281</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2937,17 +2937,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
+          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2972,44 +2972,44 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
+          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>98</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3041,27 +3041,27 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
+          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>924</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3098,27 +3098,27 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
+          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3155,32 +3155,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3190,49 +3190,49 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>743</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>361</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3247,54 +3247,54 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3304,49 +3304,49 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>360</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3361,49 +3361,49 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
+          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3440,27 +3440,27 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AI 범죄 대응 범부처 협의체 출범</t>
+          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3497,32 +3497,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
+          <t>AI 범죄 대응 범부처 협의체 출범</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3532,49 +3532,49 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>359</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3589,49 +3589,49 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
+          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>2754</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3668,32 +3668,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
+          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3703,54 +3703,54 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>7681</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>358</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
+          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>7681</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3782,32 +3782,32 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>357</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
+          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3839,32 +3839,32 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>356</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>11169</t>
+          <t>9023</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3896,12 +3896,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>352</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3911,17 +3911,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>13472</t>
+          <t>11169</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3953,27 +3953,27 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>354</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>13472</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4010,55 +4010,112 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>신기술개인정보과</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>9724</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>353</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>「개인정보 처리 방법에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12127</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>전략기획팀</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
         <is>
           <t>11519</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>공지사항</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>

--- a/docs/snapshot/downloads/pipc.xlsx
+++ b/docs/snapshot/downloads/pipc.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K65"/>
+  <dimension ref="A1:K66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,32 +476,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>35591</t>
+          <t>39131</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>380</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
+          <t>(대법원) 스크래핑 차단 한시적 유예 신청(~8.31.) 안내</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -521,19 +521,19 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-08-14 18:16:08.177242+09:00</t>
+          <t>2026-08-19 11:16:06.252027+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-14 18:16:08.177242+09:00</t>
+          <t>2026-08-19 11:16:06.252027+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>34711</t>
+          <t>35591</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -543,22 +543,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>「국경 간 개인정보 보호 규칙 인증제도의 운영에 관한 지침」 일부개정안 행정예고</t>
+          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -578,39 +578,39 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-13 17:31:09.311303+09:00</t>
+          <t>2026-08-14 18:16:08.177242+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-13 17:31:09.311303+09:00</t>
+          <t>2026-08-14 18:16:08.177242+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>34691</t>
+          <t>34711</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>379</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
+          <t>「국경 간 개인정보 보호 규칙 인증제도의 운영에 관한 지침」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12375</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -620,12 +620,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -635,39 +635,39 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-08-13 17:16:11.373869+09:00</t>
+          <t>2026-08-13 17:31:09.311303+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-08-13 17:16:11.373869+09:00</t>
+          <t>2026-08-13 17:31:09.311303+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>34071</t>
+          <t>34691</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>378</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
+          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12375</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -677,12 +677,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -692,44 +692,44 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:08.209725+09:00</t>
+          <t>2026-08-13 17:16:11.373869+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:08.209725+09:00</t>
+          <t>2026-08-13 17:16:11.373869+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>32571</t>
+          <t>34071</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>377</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
+          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -749,39 +749,39 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-08-11 11:16:08.723253+09:00</t>
+          <t>2026-08-13 09:31:08.209725+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-08-11 11:16:08.723253+09:00</t>
+          <t>2026-08-13 09:31:08.209725+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>32541</t>
+          <t>32571</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>376</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -796,106 +796,106 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-08-11 11:00:26.976860+09:00</t>
+          <t>2026-08-11 11:16:08.723253+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-08-11 11:00:26.976860+09:00</t>
+          <t>2026-08-11 11:16:08.723253+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>28831</t>
+          <t>32541</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제3자 제공사항 알림</t>
+          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-08-06 15:46:06.392884+09:00</t>
+          <t>2026-08-11 11:00:26.976860+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-08-06 15:46:06.392884+09:00</t>
+          <t>2026-08-11 11:00:26.976860+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>28361</t>
+          <t>28831</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>375</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>인공지능(AI) 시대 개인정보 제도 혁신, 국민과 함께 설계한다</t>
+          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12361</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -905,59 +905,59 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-08-06 10:00:26.758706+09:00</t>
+          <t>2026-08-06 15:46:06.392884+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-08-06 10:00:26.758706+09:00</t>
+          <t>2026-08-06 15:46:06.392884+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>22661</t>
+          <t>28361</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>개인정보위, ‘㈜KT의개인정보 유출사고’ 제재처분 의결</t>
+          <t>인공지능(AI) 시대 개인정보 제도 혁신, 국민과 함께 설계한다</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12349</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12361</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -977,44 +977,44 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30:27.268351+09:00</t>
+          <t>2026-08-06 10:00:26.758706+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30:27.268351+09:00</t>
+          <t>2026-08-06 10:00:26.758706+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>22391</t>
+          <t>22661</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>개인정보 영향평가기관 지정갱신 공고</t>
+          <t>개인정보위, ‘㈜KT의개인정보 유출사고’ 제재처분 의결</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12349</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1024,29 +1024,29 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>22351</t>
+          <t>22391</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1091,44 +1091,44 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>17701</t>
+          <t>22351</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>374</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
+          <t>개인정보 영향평가기관 지정갱신 공고</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1138,54 +1138,54 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>17362</t>
+          <t>17701</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
+          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1205,39 +1205,39 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>16883</t>
+          <t>17362</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
+          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1262,34 +1262,34 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>16882</t>
+          <t>16883</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
+          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1331,27 +1331,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>16881</t>
+          <t>16882</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
+          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1388,32 +1388,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>16314</t>
+          <t>16881</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
+          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1423,44 +1423,44 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>16313</t>
+          <t>16314</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>370</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
+          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1502,22 +1502,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>16312</t>
+          <t>16313</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>371</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
+          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1559,22 +1559,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>16311</t>
+          <t>16312</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>372</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
+          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1616,32 +1616,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>14451</t>
+          <t>16311</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>373</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
+          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1661,39 +1661,39 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>14433</t>
+          <t>14451</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>369</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1718,34 +1718,34 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>14422</t>
+          <t>14433</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>366</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1765,49 +1765,49 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14422</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
+          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1844,32 +1844,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>11392</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
+          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1879,44 +1879,44 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>11391</t>
+          <t>11392</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>367</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
+          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1958,27 +1958,27 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>11221</t>
+          <t>11391</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>368</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
+          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1993,54 +1993,54 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>11221</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
+          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2060,44 +2060,44 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>9501</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>인프라표준화팀</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2117,44 +2117,44 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>9381</t>
+          <t>9501</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
+          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>인프라표준화팀</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2174,39 +2174,39 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>9271</t>
+          <t>9381</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
+          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>법무감사담당관</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2216,116 +2216,116 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>303</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>6541</t>
+          <t>9271</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>365</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
+          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>법무감사담당관</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5491</t>
+          <t>6541</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
+          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2335,49 +2335,49 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>364</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
+          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>장석인</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2392,49 +2392,49 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
+          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>장석인</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2471,27 +2471,27 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
+          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2506,54 +2506,54 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>5391</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>363</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
+          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2563,54 +2563,54 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
+          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2620,49 +2620,49 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>362</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
+          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2677,49 +2677,49 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
+          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2756,32 +2756,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
+          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2801,39 +2801,39 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
+          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2858,39 +2858,39 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2915,44 +2915,44 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>561</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
+          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2972,19 +2972,19 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>281</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2994,17 +2994,17 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
+          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3029,44 +3029,44 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
+          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>98</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3098,27 +3098,27 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
+          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>924</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3155,27 +3155,27 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
+          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3212,32 +3212,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3247,49 +3247,49 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>743</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>361</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3304,54 +3304,54 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3361,49 +3361,49 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>360</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3418,49 +3418,49 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
+          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3497,27 +3497,27 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AI 범죄 대응 범부처 협의체 출범</t>
+          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3554,32 +3554,32 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
+          <t>AI 범죄 대응 범부처 협의체 출범</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3589,49 +3589,49 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>359</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3646,49 +3646,49 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
+          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>2754</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3725,32 +3725,32 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
+          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3760,54 +3760,54 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>7681</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>358</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
+          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>7681</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3839,32 +3839,32 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>357</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
+          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3896,32 +3896,32 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>356</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>11169</t>
+          <t>9023</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3953,12 +3953,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>352</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3968,17 +3968,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>13472</t>
+          <t>11169</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4010,27 +4010,27 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>354</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>13472</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4067,55 +4067,112 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>신기술개인정보과</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>9724</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>353</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>「개인정보 처리 방법에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12127</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>전략기획팀</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
         <is>
           <t>11519</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t>공지사항</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="K66" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>

--- a/docs/snapshot/downloads/pipc.xlsx
+++ b/docs/snapshot/downloads/pipc.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K66"/>
+  <dimension ref="A1:K67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,32 +476,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>39131</t>
+          <t>40381</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>(대법원) 스크래핑 차단 한시적 유예 신청(~8.31.) 안내</t>
+          <t>안전한 인공지능 개발을 위한 개인정보 활용 특례 신설 「개인정보 보호법」 개정안 국회 본회의 통과</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -511,54 +511,54 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-08-19 11:16:06.252027+09:00</t>
+          <t>2026-08-20 16:45:27.227566+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-19 11:16:06.252027+09:00</t>
+          <t>2026-08-20 16:45:27.227566+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>35591</t>
+          <t>39131</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>380</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
+          <t>(대법원) 스크래핑 차단 한시적 유예 신청(~8.31.) 안내</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -578,19 +578,19 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-14 18:16:08.177242+09:00</t>
+          <t>2026-08-19 11:16:06.252027+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-14 18:16:08.177242+09:00</t>
+          <t>2026-08-19 11:16:06.252027+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>34711</t>
+          <t>35591</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -600,22 +600,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>「국경 간 개인정보 보호 규칙 인증제도의 운영에 관한 지침」 일부개정안 행정예고</t>
+          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -635,39 +635,39 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-08-13 17:31:09.311303+09:00</t>
+          <t>2026-08-14 18:16:08.177242+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-08-13 17:31:09.311303+09:00</t>
+          <t>2026-08-14 18:16:08.177242+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>34691</t>
+          <t>34711</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>379</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
+          <t>「국경 간 개인정보 보호 규칙 인증제도의 운영에 관한 지침」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12375</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -677,12 +677,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -692,39 +692,39 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-08-13 17:16:11.373869+09:00</t>
+          <t>2026-08-13 17:31:09.311303+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-08-13 17:16:11.373869+09:00</t>
+          <t>2026-08-13 17:31:09.311303+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>34071</t>
+          <t>34691</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>378</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
+          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12375</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -734,12 +734,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -749,44 +749,44 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:08.209725+09:00</t>
+          <t>2026-08-13 17:16:11.373869+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:08.209725+09:00</t>
+          <t>2026-08-13 17:16:11.373869+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>32571</t>
+          <t>34071</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>377</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
+          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -806,39 +806,39 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-08-11 11:16:08.723253+09:00</t>
+          <t>2026-08-13 09:31:08.209725+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-08-11 11:16:08.723253+09:00</t>
+          <t>2026-08-13 09:31:08.209725+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>32541</t>
+          <t>32571</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>376</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -853,106 +853,106 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-08-11 11:00:26.976860+09:00</t>
+          <t>2026-08-11 11:16:08.723253+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-08-11 11:00:26.976860+09:00</t>
+          <t>2026-08-11 11:16:08.723253+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>28831</t>
+          <t>32541</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제3자 제공사항 알림</t>
+          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-08-06 15:46:06.392884+09:00</t>
+          <t>2026-08-11 11:00:26.976860+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-08-06 15:46:06.392884+09:00</t>
+          <t>2026-08-11 11:00:26.976860+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>28361</t>
+          <t>28831</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>375</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>인공지능(AI) 시대 개인정보 제도 혁신, 국민과 함께 설계한다</t>
+          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12361</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -962,59 +962,59 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-08-06 10:00:26.758706+09:00</t>
+          <t>2026-08-06 15:46:06.392884+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-08-06 10:00:26.758706+09:00</t>
+          <t>2026-08-06 15:46:06.392884+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>22661</t>
+          <t>28361</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>개인정보위, ‘㈜KT의개인정보 유출사고’ 제재처분 의결</t>
+          <t>인공지능(AI) 시대 개인정보 제도 혁신, 국민과 함께 설계한다</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12349</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12361</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1034,44 +1034,44 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30:27.268351+09:00</t>
+          <t>2026-08-06 10:00:26.758706+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30:27.268351+09:00</t>
+          <t>2026-08-06 10:00:26.758706+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>22391</t>
+          <t>22661</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>개인정보 영향평가기관 지정갱신 공고</t>
+          <t>개인정보위, ‘㈜KT의개인정보 유출사고’ 제재처분 의결</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12349</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1081,29 +1081,29 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>22351</t>
+          <t>22391</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1148,44 +1148,44 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>17701</t>
+          <t>22351</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>374</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
+          <t>개인정보 영향평가기관 지정갱신 공고</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1195,54 +1195,54 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>17362</t>
+          <t>17701</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
+          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1262,39 +1262,39 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>16883</t>
+          <t>17362</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
+          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1319,34 +1319,34 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>16882</t>
+          <t>16883</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
+          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1388,27 +1388,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>16881</t>
+          <t>16882</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
+          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1445,32 +1445,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>16314</t>
+          <t>16881</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
+          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1480,44 +1480,44 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>16313</t>
+          <t>16314</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>370</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
+          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1559,22 +1559,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>16312</t>
+          <t>16313</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>371</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
+          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1616,22 +1616,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>16311</t>
+          <t>16312</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>372</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
+          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1673,32 +1673,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>14451</t>
+          <t>16311</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>373</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
+          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1718,39 +1718,39 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>14433</t>
+          <t>14451</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>369</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1775,34 +1775,34 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>14422</t>
+          <t>14433</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>366</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1822,49 +1822,49 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14422</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
+          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1901,32 +1901,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>11392</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
+          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1936,44 +1936,44 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>11391</t>
+          <t>11392</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>367</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
+          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2015,27 +2015,27 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>11221</t>
+          <t>11391</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>368</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
+          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2050,54 +2050,54 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>11221</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
+          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2117,44 +2117,44 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>9501</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>인프라표준화팀</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2174,44 +2174,44 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>9381</t>
+          <t>9501</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
+          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>인프라표준화팀</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2231,39 +2231,39 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>9271</t>
+          <t>9381</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
+          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>법무감사담당관</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2273,116 +2273,116 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>303</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>6541</t>
+          <t>9271</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>365</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
+          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>법무감사담당관</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>5491</t>
+          <t>6541</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
+          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2392,49 +2392,49 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>364</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
+          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>장석인</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2449,49 +2449,49 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
+          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>장석인</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2528,27 +2528,27 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
+          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2563,54 +2563,54 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>5391</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>363</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
+          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2620,54 +2620,54 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
+          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2677,49 +2677,49 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>362</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
+          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2734,49 +2734,49 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
+          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2813,32 +2813,32 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
+          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2858,39 +2858,39 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
+          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2915,39 +2915,39 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2972,44 +2972,44 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>561</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
+          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3029,19 +3029,19 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>281</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3051,17 +3051,17 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
+          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3086,44 +3086,44 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
+          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>98</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3155,27 +3155,27 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
+          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>924</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3212,27 +3212,27 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
+          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3269,32 +3269,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3304,49 +3304,49 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>743</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>361</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3361,54 +3361,54 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3418,49 +3418,49 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>360</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3475,49 +3475,49 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
+          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3554,27 +3554,27 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AI 범죄 대응 범부처 협의체 출범</t>
+          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3611,32 +3611,32 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
+          <t>AI 범죄 대응 범부처 협의체 출범</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3646,49 +3646,49 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>359</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3703,49 +3703,49 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
+          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>2754</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3782,32 +3782,32 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
+          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3817,54 +3817,54 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>7681</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>358</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
+          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>7681</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3896,32 +3896,32 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>357</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
+          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3953,32 +3953,32 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>356</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>11169</t>
+          <t>9023</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4010,12 +4010,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>352</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4025,17 +4025,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>13472</t>
+          <t>11169</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4067,27 +4067,27 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>354</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>13472</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4124,55 +4124,112 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>신기술개인정보과</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>9724</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>353</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>「개인정보 처리 방법에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12127</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>전략기획팀</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
         <is>
           <t>11519</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t>공지사항</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="K67" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>

--- a/docs/snapshot/downloads/pipc.xlsx
+++ b/docs/snapshot/downloads/pipc.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K67"/>
+  <dimension ref="A1:K68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,32 +476,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>40381</t>
+          <t>43121</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>안전한 인공지능 개발을 위한 개인정보 활용 특례 신설 「개인정보 보호법」 개정안 국회 본회의 통과</t>
+          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -511,7 +511,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -521,44 +521,44 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:45:27.227566+09:00</t>
+          <t>2026-08-24 10:00:26.766249+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:45:27.227566+09:00</t>
+          <t>2026-08-24 10:00:26.766249+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>39131</t>
+          <t>40381</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>(대법원) 스크래핑 차단 한시적 유예 신청(~8.31.) 안내</t>
+          <t>안전한 인공지능 개발을 위한 개인정보 활용 특례 신설 「개인정보 보호법」 개정안 국회 본회의 통과</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -568,54 +568,54 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-19 11:16:06.252027+09:00</t>
+          <t>2026-08-20 16:45:27.227566+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-19 11:16:06.252027+09:00</t>
+          <t>2026-08-20 16:45:27.227566+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>35591</t>
+          <t>39131</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>380</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
+          <t>(대법원) 스크래핑 차단 한시적 유예 신청(~8.31.) 안내</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -635,19 +635,19 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-08-14 18:16:08.177242+09:00</t>
+          <t>2026-08-19 11:16:06.252027+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-08-14 18:16:08.177242+09:00</t>
+          <t>2026-08-19 11:16:06.252027+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>34711</t>
+          <t>35591</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -657,22 +657,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>「국경 간 개인정보 보호 규칙 인증제도의 운영에 관한 지침」 일부개정안 행정예고</t>
+          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -692,39 +692,39 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-08-13 17:31:09.311303+09:00</t>
+          <t>2026-08-14 18:16:08.177242+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-08-13 17:31:09.311303+09:00</t>
+          <t>2026-08-14 18:16:08.177242+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>34691</t>
+          <t>34711</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>379</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
+          <t>「국경 간 개인정보 보호 규칙 인증제도의 운영에 관한 지침」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12375</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -734,12 +734,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -749,39 +749,39 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-08-13 17:16:11.373869+09:00</t>
+          <t>2026-08-13 17:31:09.311303+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-08-13 17:16:11.373869+09:00</t>
+          <t>2026-08-13 17:31:09.311303+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>34071</t>
+          <t>34691</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>378</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
+          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12375</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -806,44 +806,44 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:08.209725+09:00</t>
+          <t>2026-08-13 17:16:11.373869+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:08.209725+09:00</t>
+          <t>2026-08-13 17:16:11.373869+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>32571</t>
+          <t>34071</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>377</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
+          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -863,39 +863,39 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-08-11 11:16:08.723253+09:00</t>
+          <t>2026-08-13 09:31:08.209725+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-08-11 11:16:08.723253+09:00</t>
+          <t>2026-08-13 09:31:08.209725+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>32541</t>
+          <t>32571</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>376</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -910,106 +910,106 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-08-11 11:00:26.976860+09:00</t>
+          <t>2026-08-11 11:16:08.723253+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-08-11 11:00:26.976860+09:00</t>
+          <t>2026-08-11 11:16:08.723253+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>28831</t>
+          <t>32541</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제3자 제공사항 알림</t>
+          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-08-06 15:46:06.392884+09:00</t>
+          <t>2026-08-11 11:00:26.976860+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-08-06 15:46:06.392884+09:00</t>
+          <t>2026-08-11 11:00:26.976860+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>28361</t>
+          <t>28831</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>375</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>인공지능(AI) 시대 개인정보 제도 혁신, 국민과 함께 설계한다</t>
+          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12361</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1019,59 +1019,59 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-08-06 10:00:26.758706+09:00</t>
+          <t>2026-08-06 15:46:06.392884+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-08-06 10:00:26.758706+09:00</t>
+          <t>2026-08-06 15:46:06.392884+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>22661</t>
+          <t>28361</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>개인정보위, ‘㈜KT의개인정보 유출사고’ 제재처분 의결</t>
+          <t>인공지능(AI) 시대 개인정보 제도 혁신, 국민과 함께 설계한다</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12349</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12361</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1091,44 +1091,44 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30:27.268351+09:00</t>
+          <t>2026-08-06 10:00:26.758706+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30:27.268351+09:00</t>
+          <t>2026-08-06 10:00:26.758706+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>22391</t>
+          <t>22661</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>개인정보 영향평가기관 지정갱신 공고</t>
+          <t>개인정보위, ‘㈜KT의개인정보 유출사고’ 제재처분 의결</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12349</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1138,29 +1138,29 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>22351</t>
+          <t>22391</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1205,44 +1205,44 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>17701</t>
+          <t>22351</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>374</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
+          <t>개인정보 영향평가기관 지정갱신 공고</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1252,54 +1252,54 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>17362</t>
+          <t>17701</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
+          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1319,39 +1319,39 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>16883</t>
+          <t>17362</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
+          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1376,34 +1376,34 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>16882</t>
+          <t>16883</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
+          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1445,27 +1445,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>16881</t>
+          <t>16882</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
+          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1502,32 +1502,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>16314</t>
+          <t>16881</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
+          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1537,44 +1537,44 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>16313</t>
+          <t>16314</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>370</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
+          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1616,22 +1616,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>16312</t>
+          <t>16313</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>371</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
+          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1673,22 +1673,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>16311</t>
+          <t>16312</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>372</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
+          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1730,32 +1730,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>14451</t>
+          <t>16311</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>373</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
+          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1775,39 +1775,39 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>14433</t>
+          <t>14451</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>369</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1832,34 +1832,34 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>14422</t>
+          <t>14433</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>366</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1879,49 +1879,49 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14422</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
+          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1958,32 +1958,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>11392</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
+          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1993,44 +1993,44 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>11391</t>
+          <t>11392</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>367</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
+          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2072,27 +2072,27 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>11221</t>
+          <t>11391</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>368</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
+          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2107,54 +2107,54 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>11221</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
+          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2174,44 +2174,44 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>9501</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>인프라표준화팀</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2231,44 +2231,44 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>9381</t>
+          <t>9501</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
+          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>인프라표준화팀</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2288,39 +2288,39 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>9271</t>
+          <t>9381</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
+          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>법무감사담당관</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2330,116 +2330,116 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>303</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>6541</t>
+          <t>9271</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>365</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
+          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>법무감사담당관</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5491</t>
+          <t>6541</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
+          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2449,49 +2449,49 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>364</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
+          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>장석인</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2506,49 +2506,49 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
+          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>장석인</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2585,27 +2585,27 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
+          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2620,54 +2620,54 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>5391</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>363</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
+          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2677,54 +2677,54 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
+          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2734,49 +2734,49 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>362</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
+          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2791,49 +2791,49 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
+          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2870,32 +2870,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
+          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2915,39 +2915,39 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
+          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2972,39 +2972,39 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3029,44 +3029,44 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>561</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
+          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3086,19 +3086,19 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>281</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3108,17 +3108,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
+          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3143,44 +3143,44 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
+          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>98</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3212,27 +3212,27 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
+          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>924</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3269,27 +3269,27 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
+          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3326,32 +3326,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3361,49 +3361,49 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>743</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>361</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3418,54 +3418,54 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3475,49 +3475,49 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>360</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3532,49 +3532,49 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
+          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3611,27 +3611,27 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AI 범죄 대응 범부처 협의체 출범</t>
+          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3668,32 +3668,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
+          <t>AI 범죄 대응 범부처 협의체 출범</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3703,49 +3703,49 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>359</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3760,49 +3760,49 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
+          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>2754</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3839,32 +3839,32 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
+          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3874,54 +3874,54 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>7681</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>358</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
+          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>7681</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3953,32 +3953,32 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>357</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
+          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4010,32 +4010,32 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>356</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>11169</t>
+          <t>9023</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4067,12 +4067,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>352</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4082,17 +4082,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>13472</t>
+          <t>11169</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4124,27 +4124,27 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>354</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>13472</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4181,55 +4181,112 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>신기술개인정보과</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>9724</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>353</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>「개인정보 처리 방법에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12127</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>전략기획팀</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
         <is>
           <t>11519</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t>공지사항</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="K68" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>

--- a/docs/snapshot/downloads/pipc.xlsx
+++ b/docs/snapshot/downloads/pipc.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K68"/>
+  <dimension ref="A1:K70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,27 +476,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>43121</t>
+          <t>43452</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>381</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
+          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -511,54 +511,54 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-08-24 10:00:26.766249+09:00</t>
+          <t>2026-08-24 14:01:07.394147+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-24 10:00:26.766249+09:00</t>
+          <t>2026-08-24 14:01:07.394147+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>40381</t>
+          <t>43451</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>382</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>안전한 인공지능 개발을 위한 개인정보 활용 특례 신설 「개인정보 보호법」 개정안 국회 본회의 통과</t>
+          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -568,54 +568,54 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-20 16:45:27.227566+09:00</t>
+          <t>2026-08-24 14:01:07.394147+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-20 16:45:27.227566+09:00</t>
+          <t>2026-08-24 14:01:07.394147+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>39131</t>
+          <t>43121</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>(대법원) 스크래핑 차단 한시적 유예 신청(~8.31.) 안내</t>
+          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -625,54 +625,54 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-08-19 11:16:06.252027+09:00</t>
+          <t>2026-08-24 10:00:26.766249+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-08-19 11:16:06.252027+09:00</t>
+          <t>2026-08-24 10:00:26.766249+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>35591</t>
+          <t>40381</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
+          <t>안전한 인공지능 개발을 위한 개인정보 활용 특례 신설 「개인정보 보호법」 개정안 국회 본회의 통과</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -682,54 +682,54 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-08-14 18:16:08.177242+09:00</t>
+          <t>2026-08-20 16:45:27.227566+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-08-14 18:16:08.177242+09:00</t>
+          <t>2026-08-20 16:45:27.227566+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>34711</t>
+          <t>39131</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>380</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>「국경 간 개인정보 보호 규칙 인증제도의 운영에 관한 지침」 일부개정안 행정예고</t>
+          <t>(대법원) 스크래핑 차단 한시적 유예 신청(~8.31.) 안내</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -749,24 +749,24 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-08-13 17:31:09.311303+09:00</t>
+          <t>2026-08-19 11:16:06.252027+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-08-13 17:31:09.311303+09:00</t>
+          <t>2026-08-19 11:16:06.252027+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>34691</t>
+          <t>35591</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>379</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12375</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -786,17 +786,17 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -806,39 +806,39 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-08-13 17:16:11.373869+09:00</t>
+          <t>2026-08-14 18:16:08.177242+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-08-13 17:16:11.373869+09:00</t>
+          <t>2026-08-14 18:16:08.177242+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>34071</t>
+          <t>34711</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>379</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
+          <t>「국경 간 개인정보 보호 규칙 인증제도의 운영에 관한 지침」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -863,54 +863,54 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:08.209725+09:00</t>
+          <t>2026-08-13 17:31:09.311303+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:08.209725+09:00</t>
+          <t>2026-08-13 17:31:09.311303+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>32571</t>
+          <t>34691</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>378</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
+          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12375</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -920,44 +920,44 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-08-11 11:16:08.723253+09:00</t>
+          <t>2026-08-13 17:16:11.373869+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-08-11 11:16:08.723253+09:00</t>
+          <t>2026-08-13 17:16:11.373869+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>32541</t>
+          <t>34071</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>377</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
+          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -967,64 +967,64 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-08-11 11:00:26.976860+09:00</t>
+          <t>2026-08-13 09:31:08.209725+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-08-11 11:00:26.976860+09:00</t>
+          <t>2026-08-13 09:31:08.209725+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>28831</t>
+          <t>32571</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>376</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제3자 제공사항 알림</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1034,44 +1034,44 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-08-06 15:46:06.392884+09:00</t>
+          <t>2026-08-11 11:16:08.723253+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-08-06 15:46:06.392884+09:00</t>
+          <t>2026-08-11 11:16:08.723253+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>28361</t>
+          <t>32541</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>인공지능(AI) 시대 개인정보 제도 혁신, 국민과 함께 설계한다</t>
+          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12361</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1091,101 +1091,101 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-08-06 10:00:26.758706+09:00</t>
+          <t>2026-08-11 11:00:26.976860+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-08-06 10:00:26.758706+09:00</t>
+          <t>2026-08-11 11:00:26.976860+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>22661</t>
+          <t>28831</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>375</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>개인정보위, ‘㈜KT의개인정보 유출사고’ 제재처분 의결</t>
+          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12349</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30:27.268351+09:00</t>
+          <t>2026-08-06 15:46:06.392884+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30:27.268351+09:00</t>
+          <t>2026-08-06 15:46:06.392884+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>22391</t>
+          <t>28361</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>개인정보 영향평가기관 지정갱신 공고</t>
+          <t>인공지능(AI) 시대 개인정보 제도 혁신, 국민과 함께 설계한다</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12361</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1195,54 +1195,54 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-08-06 10:00:26.758706+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-08-06 10:00:26.758706+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>22351</t>
+          <t>22661</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>개인정보 영향평가기관 지정갱신 공고</t>
+          <t>개인정보위, ‘㈜KT의개인정보 유출사고’ 제재처분 의결</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12349</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1252,54 +1252,54 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>17701</t>
+          <t>22391</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>374</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
+          <t>개인정보 영향평가기관 지정갱신 공고</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1309,54 +1309,54 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>17362</t>
+          <t>22351</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>374</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
+          <t>개인정보 영향평가기관 지정갱신 공고</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1366,54 +1366,54 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>16883</t>
+          <t>17701</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
+          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1433,19 +1433,19 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>16882</t>
+          <t>17362</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1455,17 +1455,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
+          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1490,39 +1490,39 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>16881</t>
+          <t>16883</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
+          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1559,32 +1559,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>16314</t>
+          <t>16882</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
+          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1594,54 +1594,54 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>16313</t>
+          <t>16881</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
+          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1651,44 +1651,44 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>16312</t>
+          <t>16314</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>370</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
+          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1730,22 +1730,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>16311</t>
+          <t>16313</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>371</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
+          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1787,32 +1787,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>14451</t>
+          <t>16312</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>372</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
+          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1832,44 +1832,44 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>14433</t>
+          <t>16311</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>373</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1889,39 +1889,39 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>14422</t>
+          <t>14451</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>369</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1936,49 +1936,49 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14433</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>366</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1993,54 +1993,54 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>11392</t>
+          <t>14422</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
+          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2050,54 +2050,54 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>11391</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
+          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2107,49 +2107,49 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>11221</t>
+          <t>11392</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>367</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
+          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2164,54 +2164,54 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>11391</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>368</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
+          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2221,54 +2221,54 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>9501</t>
+          <t>11221</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
+          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>인프라표준화팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2288,19 +2288,19 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>9381</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2345,101 +2345,101 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>9271</t>
+          <t>9501</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
+          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>법무감사담당관</t>
+          <t>인프라표준화팀</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>6541</t>
+          <t>9381</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
+          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>303</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2459,54 +2459,54 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5491</t>
+          <t>9271</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>365</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
+          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>법무감사담당관</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2516,44 +2516,44 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>6541</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
+          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>장석인</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2573,34 +2573,34 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>364</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
+          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2620,49 +2620,49 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
+          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>장석인</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2677,54 +2677,54 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
+          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2744,44 +2744,44 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>5391</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>363</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
+          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2801,44 +2801,44 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
+          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2858,39 +2858,39 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>362</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
+          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2905,54 +2905,54 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
+          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2972,44 +2972,44 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
+          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3029,39 +3029,39 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
+          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3086,44 +3086,44 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3143,44 +3143,44 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>561</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
+          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3200,44 +3200,44 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>281</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
+          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3257,44 +3257,44 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
+          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>98</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3326,27 +3326,27 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
+          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>924</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3383,32 +3383,32 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
+          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3418,44 +3418,44 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>743</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3497,32 +3497,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>361</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3554,32 +3554,32 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3611,22 +3611,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>360</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3646,49 +3646,49 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AI 범죄 대응 범부처 협의체 출범</t>
+          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3725,32 +3725,32 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
+          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3760,54 +3760,54 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
+          <t>AI 범죄 대응 범부처 협의체 출범</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3839,22 +3839,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>359</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3874,54 +3874,54 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
+          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3931,54 +3931,54 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>7681</t>
+          <t>2754</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
+          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3988,44 +3988,44 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>358</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
+          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>7681</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4067,32 +4067,32 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>357</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>11169</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4124,32 +4124,32 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>356</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>13472</t>
+          <t>9023</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4181,32 +4181,32 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>352</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>11169</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4238,55 +4238,169 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>354</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>조사총괄과</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>13472</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>신기술개인정보과</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>9724</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>353</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>「개인정보 처리 방법에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12127</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>전략기획팀</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
         <is>
           <t>11519</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t>공지사항</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="K70" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>

--- a/docs/snapshot/downloads/pipc.xlsx
+++ b/docs/snapshot/downloads/pipc.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K70"/>
+  <dimension ref="A1:K71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,27 +476,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>43452</t>
+          <t>43521</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
+          <t>개인정보위, 2026년 공공기관 개인정보 보호수준 평가단 위촉</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -511,44 +511,44 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-08-24 14:01:07.394147+09:00</t>
+          <t>2026-08-24 15:00:28.011868+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-24 14:01:07.394147+09:00</t>
+          <t>2026-08-24 15:00:28.011868+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>43451</t>
+          <t>43452</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>381</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
+          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -590,27 +590,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>43121</t>
+          <t>43451</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>382</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
+          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -630,49 +630,49 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-08-24 10:00:26.766249+09:00</t>
+          <t>2026-08-24 14:01:07.394147+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-08-24 10:00:26.766249+09:00</t>
+          <t>2026-08-24 14:01:07.394147+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>40381</t>
+          <t>43121</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>안전한 인공지능 개발을 위한 개인정보 활용 특례 신설 「개인정보 보호법」 개정안 국회 본회의 통과</t>
+          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -692,44 +692,44 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-08-20 16:45:27.227566+09:00</t>
+          <t>2026-08-24 10:00:26.766249+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-08-20 16:45:27.227566+09:00</t>
+          <t>2026-08-24 10:00:26.766249+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>39131</t>
+          <t>40381</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>(대법원) 스크래핑 차단 한시적 유예 신청(~8.31.) 안내</t>
+          <t>안전한 인공지능 개발을 위한 개인정보 활용 특례 신설 「개인정보 보호법」 개정안 국회 본회의 통과</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -739,54 +739,54 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-08-19 11:16:06.252027+09:00</t>
+          <t>2026-08-20 16:45:27.227566+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-08-19 11:16:06.252027+09:00</t>
+          <t>2026-08-20 16:45:27.227566+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>35591</t>
+          <t>39131</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>380</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
+          <t>(대법원) 스크래핑 차단 한시적 유예 신청(~8.31.) 안내</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -806,19 +806,19 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-08-14 18:16:08.177242+09:00</t>
+          <t>2026-08-19 11:16:06.252027+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-08-14 18:16:08.177242+09:00</t>
+          <t>2026-08-19 11:16:06.252027+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>34711</t>
+          <t>35591</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -828,22 +828,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>「국경 간 개인정보 보호 규칙 인증제도의 운영에 관한 지침」 일부개정안 행정예고</t>
+          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -863,39 +863,39 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-08-13 17:31:09.311303+09:00</t>
+          <t>2026-08-14 18:16:08.177242+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-08-13 17:31:09.311303+09:00</t>
+          <t>2026-08-14 18:16:08.177242+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>34691</t>
+          <t>34711</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>379</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
+          <t>「국경 간 개인정보 보호 규칙 인증제도의 운영에 관한 지침」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12375</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -920,39 +920,39 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-08-13 17:16:11.373869+09:00</t>
+          <t>2026-08-13 17:31:09.311303+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-08-13 17:16:11.373869+09:00</t>
+          <t>2026-08-13 17:31:09.311303+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>34071</t>
+          <t>34691</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>378</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
+          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12375</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -962,12 +962,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -977,44 +977,44 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:08.209725+09:00</t>
+          <t>2026-08-13 17:16:11.373869+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:08.209725+09:00</t>
+          <t>2026-08-13 17:16:11.373869+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>32571</t>
+          <t>34071</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>377</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
+          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1034,39 +1034,39 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-08-11 11:16:08.723253+09:00</t>
+          <t>2026-08-13 09:31:08.209725+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-08-11 11:16:08.723253+09:00</t>
+          <t>2026-08-13 09:31:08.209725+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>32541</t>
+          <t>32571</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>376</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1081,106 +1081,106 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-08-11 11:00:26.976860+09:00</t>
+          <t>2026-08-11 11:16:08.723253+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-08-11 11:00:26.976860+09:00</t>
+          <t>2026-08-11 11:16:08.723253+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>28831</t>
+          <t>32541</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제3자 제공사항 알림</t>
+          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-08-06 15:46:06.392884+09:00</t>
+          <t>2026-08-11 11:00:26.976860+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-08-06 15:46:06.392884+09:00</t>
+          <t>2026-08-11 11:00:26.976860+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>28361</t>
+          <t>28831</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>375</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>인공지능(AI) 시대 개인정보 제도 혁신, 국민과 함께 설계한다</t>
+          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12361</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1190,59 +1190,59 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-08-06 10:00:26.758706+09:00</t>
+          <t>2026-08-06 15:46:06.392884+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-08-06 10:00:26.758706+09:00</t>
+          <t>2026-08-06 15:46:06.392884+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>22661</t>
+          <t>28361</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>개인정보위, ‘㈜KT의개인정보 유출사고’ 제재처분 의결</t>
+          <t>인공지능(AI) 시대 개인정보 제도 혁신, 국민과 함께 설계한다</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12349</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12361</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1262,44 +1262,44 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30:27.268351+09:00</t>
+          <t>2026-08-06 10:00:26.758706+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30:27.268351+09:00</t>
+          <t>2026-08-06 10:00:26.758706+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>22391</t>
+          <t>22661</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>개인정보 영향평가기관 지정갱신 공고</t>
+          <t>개인정보위, ‘㈜KT의개인정보 유출사고’ 제재처분 의결</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12349</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1309,29 +1309,29 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>22351</t>
+          <t>22391</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1376,44 +1376,44 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>17701</t>
+          <t>22351</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>374</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
+          <t>개인정보 영향평가기관 지정갱신 공고</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1423,54 +1423,54 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>17362</t>
+          <t>17701</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
+          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1490,39 +1490,39 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>16883</t>
+          <t>17362</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
+          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1547,34 +1547,34 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>16882</t>
+          <t>16883</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
+          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1616,27 +1616,27 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>16881</t>
+          <t>16882</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
+          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1673,32 +1673,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>16314</t>
+          <t>16881</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
+          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1708,44 +1708,44 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>16313</t>
+          <t>16314</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>370</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
+          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1787,22 +1787,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>16312</t>
+          <t>16313</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>371</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
+          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1844,22 +1844,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>16311</t>
+          <t>16312</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>372</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
+          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1901,32 +1901,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>14451</t>
+          <t>16311</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>373</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
+          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1946,39 +1946,39 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>14433</t>
+          <t>14451</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>369</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2003,34 +2003,34 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>14422</t>
+          <t>14433</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>366</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2050,49 +2050,49 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14422</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
+          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2129,32 +2129,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>11392</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
+          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2164,44 +2164,44 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>11391</t>
+          <t>11392</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>367</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
+          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2243,27 +2243,27 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>11221</t>
+          <t>11391</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>368</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
+          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2278,54 +2278,54 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>11221</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
+          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2345,44 +2345,44 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>9501</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>인프라표준화팀</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2402,44 +2402,44 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>9381</t>
+          <t>9501</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
+          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>인프라표준화팀</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2459,39 +2459,39 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>9271</t>
+          <t>9381</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
+          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>법무감사담당관</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2501,116 +2501,116 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>303</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>6541</t>
+          <t>9271</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>365</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
+          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>법무감사담당관</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>5491</t>
+          <t>6541</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
+          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2620,49 +2620,49 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>364</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
+          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>장석인</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2677,49 +2677,49 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
+          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>장석인</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2756,27 +2756,27 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
+          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2791,54 +2791,54 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>5391</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>363</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
+          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2848,54 +2848,54 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
+          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2905,49 +2905,49 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>362</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
+          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2962,49 +2962,49 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
+          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3041,32 +3041,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
+          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3086,39 +3086,39 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
+          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3143,39 +3143,39 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3200,44 +3200,44 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>561</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
+          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3257,19 +3257,19 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>281</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3279,17 +3279,17 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
+          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3314,44 +3314,44 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
+          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>98</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3383,27 +3383,27 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
+          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>924</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3440,27 +3440,27 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
+          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3497,32 +3497,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3532,49 +3532,49 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>743</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>361</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3589,54 +3589,54 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3646,49 +3646,49 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>360</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3703,49 +3703,49 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
+          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3782,27 +3782,27 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AI 범죄 대응 범부처 협의체 출범</t>
+          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3839,32 +3839,32 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
+          <t>AI 범죄 대응 범부처 협의체 출범</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3874,49 +3874,49 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>359</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3931,49 +3931,49 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
+          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>2754</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4010,32 +4010,32 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
+          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4045,54 +4045,54 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>7681</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>358</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
+          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>7681</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4124,32 +4124,32 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>357</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
+          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4181,32 +4181,32 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>356</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>11169</t>
+          <t>9023</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4238,12 +4238,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>352</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4253,17 +4253,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>13472</t>
+          <t>11169</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4295,27 +4295,27 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>354</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>13472</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4352,55 +4352,112 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>신기술개인정보과</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>9724</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>353</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>「개인정보 처리 방법에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12127</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>전략기획팀</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
         <is>
           <t>11519</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t>공지사항</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
+      <c r="J71" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
+      <c r="K71" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>

--- a/docs/snapshot/downloads/pipc.xlsx
+++ b/docs/snapshot/downloads/pipc.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K71"/>
+  <dimension ref="A1:K72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,22 +476,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>43521</t>
+          <t>44101</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>개인정보위, 2026년 공공기관 개인정보 보호수준 평가단 위촉</t>
+          <t>정부, 공공부문 개인정보 보호 역량 강화 위한 인력 확충한다</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -501,7 +501,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -511,7 +511,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -521,39 +521,39 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-08-24 15:00:28.011868+09:00</t>
+          <t>2026-08-25 12:00:28.630385+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-24 15:00:28.011868+09:00</t>
+          <t>2026-08-25 12:00:28.630385+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>43452</t>
+          <t>43521</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
+          <t>개인정보위, 2026년 공공기관 개인정보 보호수준 평가단 위촉</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -568,44 +568,44 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-24 14:01:07.394147+09:00</t>
+          <t>2026-08-24 15:00:28.011868+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-24 14:01:07.394147+09:00</t>
+          <t>2026-08-24 15:00:28.011868+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>43451</t>
+          <t>43452</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>381</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
+          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -647,27 +647,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>43121</t>
+          <t>43451</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>382</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
+          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -687,49 +687,49 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-08-24 10:00:26.766249+09:00</t>
+          <t>2026-08-24 14:01:07.394147+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-08-24 10:00:26.766249+09:00</t>
+          <t>2026-08-24 14:01:07.394147+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>40381</t>
+          <t>43121</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>안전한 인공지능 개발을 위한 개인정보 활용 특례 신설 「개인정보 보호법」 개정안 국회 본회의 통과</t>
+          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -749,44 +749,44 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-08-20 16:45:27.227566+09:00</t>
+          <t>2026-08-24 10:00:26.766249+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-08-20 16:45:27.227566+09:00</t>
+          <t>2026-08-24 10:00:26.766249+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>39131</t>
+          <t>40381</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>(대법원) 스크래핑 차단 한시적 유예 신청(~8.31.) 안내</t>
+          <t>안전한 인공지능 개발을 위한 개인정보 활용 특례 신설 「개인정보 보호법」 개정안 국회 본회의 통과</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -796,54 +796,54 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-08-19 11:16:06.252027+09:00</t>
+          <t>2026-08-20 16:45:27.227566+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-08-19 11:16:06.252027+09:00</t>
+          <t>2026-08-20 16:45:27.227566+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>35591</t>
+          <t>39131</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>380</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
+          <t>(대법원) 스크래핑 차단 한시적 유예 신청(~8.31.) 안내</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -863,19 +863,19 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-08-14 18:16:08.177242+09:00</t>
+          <t>2026-08-19 11:16:06.252027+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-08-14 18:16:08.177242+09:00</t>
+          <t>2026-08-19 11:16:06.252027+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>34711</t>
+          <t>35591</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -885,22 +885,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>「국경 간 개인정보 보호 규칙 인증제도의 운영에 관한 지침」 일부개정안 행정예고</t>
+          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -920,39 +920,39 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-08-13 17:31:09.311303+09:00</t>
+          <t>2026-08-14 18:16:08.177242+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-08-13 17:31:09.311303+09:00</t>
+          <t>2026-08-14 18:16:08.177242+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>34691</t>
+          <t>34711</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>379</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
+          <t>「국경 간 개인정보 보호 규칙 인증제도의 운영에 관한 지침」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12375</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -962,12 +962,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -977,39 +977,39 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-08-13 17:16:11.373869+09:00</t>
+          <t>2026-08-13 17:31:09.311303+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-08-13 17:16:11.373869+09:00</t>
+          <t>2026-08-13 17:31:09.311303+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>34071</t>
+          <t>34691</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>378</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
+          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12375</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1019,12 +1019,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1034,44 +1034,44 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:08.209725+09:00</t>
+          <t>2026-08-13 17:16:11.373869+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:08.209725+09:00</t>
+          <t>2026-08-13 17:16:11.373869+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>32571</t>
+          <t>34071</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>377</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
+          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1091,39 +1091,39 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-08-11 11:16:08.723253+09:00</t>
+          <t>2026-08-13 09:31:08.209725+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-08-11 11:16:08.723253+09:00</t>
+          <t>2026-08-13 09:31:08.209725+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>32541</t>
+          <t>32571</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>376</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1138,106 +1138,106 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-08-11 11:00:26.976860+09:00</t>
+          <t>2026-08-11 11:16:08.723253+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-08-11 11:00:26.976860+09:00</t>
+          <t>2026-08-11 11:16:08.723253+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>28831</t>
+          <t>32541</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제3자 제공사항 알림</t>
+          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-08-06 15:46:06.392884+09:00</t>
+          <t>2026-08-11 11:00:26.976860+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-08-06 15:46:06.392884+09:00</t>
+          <t>2026-08-11 11:00:26.976860+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>28361</t>
+          <t>28831</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>375</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>인공지능(AI) 시대 개인정보 제도 혁신, 국민과 함께 설계한다</t>
+          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12361</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1247,59 +1247,59 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-08-06 10:00:26.758706+09:00</t>
+          <t>2026-08-06 15:46:06.392884+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-08-06 10:00:26.758706+09:00</t>
+          <t>2026-08-06 15:46:06.392884+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>22661</t>
+          <t>28361</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>개인정보위, ‘㈜KT의개인정보 유출사고’ 제재처분 의결</t>
+          <t>인공지능(AI) 시대 개인정보 제도 혁신, 국민과 함께 설계한다</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12349</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12361</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1319,44 +1319,44 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30:27.268351+09:00</t>
+          <t>2026-08-06 10:00:26.758706+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30:27.268351+09:00</t>
+          <t>2026-08-06 10:00:26.758706+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>22391</t>
+          <t>22661</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>개인정보 영향평가기관 지정갱신 공고</t>
+          <t>개인정보위, ‘㈜KT의개인정보 유출사고’ 제재처분 의결</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12349</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1366,29 +1366,29 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>22351</t>
+          <t>22391</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1433,44 +1433,44 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>17701</t>
+          <t>22351</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>374</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
+          <t>개인정보 영향평가기관 지정갱신 공고</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1480,54 +1480,54 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>17362</t>
+          <t>17701</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
+          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1547,39 +1547,39 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>16883</t>
+          <t>17362</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
+          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1604,34 +1604,34 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>16882</t>
+          <t>16883</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
+          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1673,27 +1673,27 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>16881</t>
+          <t>16882</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
+          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1730,32 +1730,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>16314</t>
+          <t>16881</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
+          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1765,44 +1765,44 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>16313</t>
+          <t>16314</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>370</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
+          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1844,22 +1844,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>16312</t>
+          <t>16313</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>371</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
+          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1901,22 +1901,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>16311</t>
+          <t>16312</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>372</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
+          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1958,32 +1958,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>14451</t>
+          <t>16311</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>373</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
+          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2003,39 +2003,39 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>14433</t>
+          <t>14451</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>369</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2060,34 +2060,34 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>14422</t>
+          <t>14433</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>366</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2107,49 +2107,49 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14422</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
+          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2186,32 +2186,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>11392</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
+          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2221,44 +2221,44 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>11391</t>
+          <t>11392</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>367</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
+          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2300,27 +2300,27 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>11221</t>
+          <t>11391</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>368</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
+          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2335,54 +2335,54 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>11221</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
+          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2402,44 +2402,44 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>9501</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>인프라표준화팀</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2459,44 +2459,44 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>9381</t>
+          <t>9501</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
+          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>인프라표준화팀</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2516,39 +2516,39 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>9271</t>
+          <t>9381</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
+          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>법무감사담당관</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2558,116 +2558,116 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>303</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>6541</t>
+          <t>9271</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>365</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
+          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>법무감사담당관</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5491</t>
+          <t>6541</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
+          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2677,49 +2677,49 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>364</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
+          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>장석인</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2734,49 +2734,49 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
+          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>장석인</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2813,27 +2813,27 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
+          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2848,54 +2848,54 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>5391</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>363</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
+          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2905,54 +2905,54 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
+          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2962,49 +2962,49 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>362</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
+          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3019,49 +3019,49 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
+          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3098,32 +3098,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
+          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3143,39 +3143,39 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
+          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3200,39 +3200,39 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3257,44 +3257,44 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>561</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
+          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3314,19 +3314,19 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>281</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3336,17 +3336,17 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
+          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3371,44 +3371,44 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
+          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>98</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3440,27 +3440,27 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
+          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>924</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3497,27 +3497,27 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
+          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3554,32 +3554,32 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3589,49 +3589,49 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>743</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>361</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3646,54 +3646,54 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3703,49 +3703,49 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>360</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3760,49 +3760,49 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
+          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3839,27 +3839,27 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AI 범죄 대응 범부처 협의체 출범</t>
+          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3896,32 +3896,32 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
+          <t>AI 범죄 대응 범부처 협의체 출범</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3931,49 +3931,49 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>359</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3988,49 +3988,49 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
+          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>2754</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4067,32 +4067,32 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
+          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4102,54 +4102,54 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>7681</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>358</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
+          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>7681</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4181,32 +4181,32 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>357</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
+          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4238,32 +4238,32 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>356</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>11169</t>
+          <t>9023</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4295,12 +4295,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>352</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4310,17 +4310,17 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>13472</t>
+          <t>11169</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4352,27 +4352,27 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>354</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>13472</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4409,55 +4409,112 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>신기술개인정보과</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>9724</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>353</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>「개인정보 처리 방법에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12127</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="E72" t="inlineStr">
         <is>
           <t>전략기획팀</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
         <is>
           <t>11519</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t>공지사항</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
+      <c r="J72" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
+      <c r="K72" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>

--- a/docs/snapshot/downloads/pipc.xlsx
+++ b/docs/snapshot/downloads/pipc.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K72"/>
+  <dimension ref="A1:K75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,32 +476,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>44101</t>
+          <t>45663</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>정부, 공공부문 개인정보 보호 역량 강화 위한 인력 확충한다</t>
+          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -511,7 +511,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -521,44 +521,44 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-08-25 12:00:28.630385+09:00</t>
+          <t>2026-08-27 11:00:26.295039+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-25 12:00:28.630385+09:00</t>
+          <t>2026-08-27 11:00:26.295039+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>43521</t>
+          <t>45662</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>개인정보위, 2026년 공공기관 개인정보 보호수준 평가단 위촉</t>
+          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -578,44 +578,44 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-24 15:00:28.011868+09:00</t>
+          <t>2026-08-27 11:00:26.295039+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-24 15:00:28.011868+09:00</t>
+          <t>2026-08-27 11:00:26.295039+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>43452</t>
+          <t>45661</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
+          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -625,54 +625,54 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-08-24 14:01:07.394147+09:00</t>
+          <t>2026-08-27 11:00:26.295039+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-08-24 14:01:07.394147+09:00</t>
+          <t>2026-08-27 11:00:26.295039+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>43451</t>
+          <t>44101</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
+          <t>정부, 공공부문 개인정보 보호 역량 강화 위한 인력 확충한다</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -682,29 +682,29 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-08-24 14:01:07.394147+09:00</t>
+          <t>2026-08-25 12:00:28.630385+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-08-24 14:01:07.394147+09:00</t>
+          <t>2026-08-25 12:00:28.630385+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>43121</t>
+          <t>43521</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
+          <t>개인정보위, 2026년 공공기관 개인정보 보호수준 평가단 위촉</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -749,44 +749,44 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-08-24 10:00:26.766249+09:00</t>
+          <t>2026-08-24 15:00:28.011868+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-08-24 10:00:26.766249+09:00</t>
+          <t>2026-08-24 15:00:28.011868+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>40381</t>
+          <t>43452</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>381</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>안전한 인공지능 개발을 위한 개인정보 활용 특례 신설 「개인정보 보호법」 개정안 국회 본회의 통과</t>
+          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -796,54 +796,54 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-08-20 16:45:27.227566+09:00</t>
+          <t>2026-08-24 14:01:07.394147+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-08-20 16:45:27.227566+09:00</t>
+          <t>2026-08-24 14:01:07.394147+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>39131</t>
+          <t>43451</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>382</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>(대법원) 스크래핑 차단 한시적 유예 신청(~8.31.) 안내</t>
+          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -863,44 +863,44 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-08-19 11:16:06.252027+09:00</t>
+          <t>2026-08-24 14:01:07.394147+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-08-19 11:16:06.252027+09:00</t>
+          <t>2026-08-24 14:01:07.394147+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>35591</t>
+          <t>43121</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
+          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -910,54 +910,54 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-08-14 18:16:08.177242+09:00</t>
+          <t>2026-08-24 10:00:26.766249+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-08-14 18:16:08.177242+09:00</t>
+          <t>2026-08-24 10:00:26.766249+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>34711</t>
+          <t>40381</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>「국경 간 개인정보 보호 규칙 인증제도의 운영에 관한 지침」 일부개정안 행정예고</t>
+          <t>안전한 인공지능 개발을 위한 개인정보 활용 특례 신설 「개인정보 보호법」 개정안 국회 본회의 통과</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -967,64 +967,64 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-08-13 17:31:09.311303+09:00</t>
+          <t>2026-08-20 16:45:27.227566+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-08-13 17:31:09.311303+09:00</t>
+          <t>2026-08-20 16:45:27.227566+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>34691</t>
+          <t>39131</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>380</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
+          <t>(대법원) 스크래핑 차단 한시적 유예 신청(~8.31.) 안내</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12375</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1034,44 +1034,44 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-08-13 17:16:11.373869+09:00</t>
+          <t>2026-08-19 11:16:06.252027+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-08-13 17:16:11.373869+09:00</t>
+          <t>2026-08-19 11:16:06.252027+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>34071</t>
+          <t>35591</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>379</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
+          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1091,44 +1091,44 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:08.209725+09:00</t>
+          <t>2026-08-14 18:16:08.177242+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:08.209725+09:00</t>
+          <t>2026-08-14 18:16:08.177242+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>32571</t>
+          <t>34711</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>379</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
+          <t>「국경 간 개인정보 보호 규칙 인증제도의 운영에 관한 지침」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1148,106 +1148,106 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-08-11 11:16:08.723253+09:00</t>
+          <t>2026-08-13 17:31:09.311303+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-08-11 11:16:08.723253+09:00</t>
+          <t>2026-08-13 17:31:09.311303+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>32541</t>
+          <t>34691</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>378</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
+          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12375</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-08-11 11:00:26.976860+09:00</t>
+          <t>2026-08-13 17:16:11.373869+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-08-11 11:00:26.976860+09:00</t>
+          <t>2026-08-13 17:16:11.373869+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>28831</t>
+          <t>34071</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>377</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제3자 제공사항 알림</t>
+          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1262,44 +1262,44 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-08-06 15:46:06.392884+09:00</t>
+          <t>2026-08-13 09:31:08.209725+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-08-06 15:46:06.392884+09:00</t>
+          <t>2026-08-13 09:31:08.209725+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>28361</t>
+          <t>32571</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>376</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>인공지능(AI) 시대 개인정보 제도 혁신, 국민과 함께 설계한다</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12361</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1309,54 +1309,54 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-08-06 10:00:26.758706+09:00</t>
+          <t>2026-08-11 11:16:08.723253+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-08-06 10:00:26.758706+09:00</t>
+          <t>2026-08-11 11:16:08.723253+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>22661</t>
+          <t>32541</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>개인정보위, ‘㈜KT의개인정보 유출사고’ 제재처분 의결</t>
+          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12349</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1376,54 +1376,54 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30:27.268351+09:00</t>
+          <t>2026-08-11 11:00:26.976860+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30:27.268351+09:00</t>
+          <t>2026-08-11 11:00:26.976860+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>22391</t>
+          <t>28831</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>375</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>개인정보 영향평가기관 지정갱신 공고</t>
+          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1433,44 +1433,44 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-08-06 15:46:06.392884+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-08-06 15:46:06.392884+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>22351</t>
+          <t>28361</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>개인정보 영향평가기관 지정갱신 공고</t>
+          <t>인공지능(AI) 시대 개인정보 제도 혁신, 국민과 함께 설계한다</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12361</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1480,54 +1480,54 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-08-06 10:00:26.758706+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-08-06 10:00:26.758706+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>17701</t>
+          <t>22661</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
+          <t>개인정보위, ‘㈜KT의개인정보 유출사고’ 제재처분 의결</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12349</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1547,44 +1547,44 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>17362</t>
+          <t>22391</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>374</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
+          <t>개인정보 영향평가기관 지정갱신 공고</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1599,49 +1599,49 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>16883</t>
+          <t>22351</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>374</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
+          <t>개인정보 영향평가기관 지정갱신 공고</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1651,54 +1651,54 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>16882</t>
+          <t>17701</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
+          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1718,39 +1718,39 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>16881</t>
+          <t>17362</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
+          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1775,44 +1775,44 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>16314</t>
+          <t>16883</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
+          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1822,54 +1822,54 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>16313</t>
+          <t>16882</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
+          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1879,54 +1879,54 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>16312</t>
+          <t>16881</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
+          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1936,44 +1936,44 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>16311</t>
+          <t>16314</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>370</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
+          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2015,32 +2015,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>14451</t>
+          <t>16313</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>371</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
+          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2060,44 +2060,44 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>14433</t>
+          <t>16312</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>372</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2117,44 +2117,44 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>14422</t>
+          <t>16311</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>373</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
+          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2169,39 +2169,39 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14451</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>369</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2221,54 +2221,54 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>11392</t>
+          <t>14433</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>366</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2288,44 +2288,44 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>11391</t>
+          <t>14422</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
+          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2340,49 +2340,49 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>11221</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
+          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2402,44 +2402,44 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>11392</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>367</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
+          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2449,54 +2449,54 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>9501</t>
+          <t>11391</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>368</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
+          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>인프라표준화팀</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2511,49 +2511,49 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>9381</t>
+          <t>11221</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
+          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2573,101 +2573,101 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>9271</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>법무감사담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>6541</t>
+          <t>9501</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
+          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>인프라표준화팀</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2687,44 +2687,44 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5491</t>
+          <t>9381</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
+          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2734,111 +2734,111 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>303</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>9271</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>365</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
+          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>장석인</t>
+          <t>법무감사담당관</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>6541</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
+          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2858,39 +2858,39 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>364</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
+          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2915,44 +2915,44 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
+          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>장석인</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2972,44 +2972,44 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
+          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3019,44 +3019,44 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>5391</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>363</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
+          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3076,54 +3076,54 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
+          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3143,44 +3143,44 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>362</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
+          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3190,54 +3190,54 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
+          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3257,44 +3257,44 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
+          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3314,44 +3314,44 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
+          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3371,56 +3371,56 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>1272</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>운영지원과</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>1269</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>조사1과</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
       <c r="I53" t="inlineStr">
         <is>
           <t>보도자료</t>
@@ -3428,44 +3428,44 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>561</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
+          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3485,44 +3485,44 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>281</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
+          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3542,44 +3542,44 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
+          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>98</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3611,32 +3611,32 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
+          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3646,54 +3646,54 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>924</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
+          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3725,32 +3725,32 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3760,54 +3760,54 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>743</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>361</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3817,54 +3817,54 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3896,27 +3896,27 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>360</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AI 범죄 대응 범부처 협의체 출범</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3931,54 +3931,54 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
+          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3988,54 +3988,54 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
+          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4067,32 +4067,32 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
+          <t>AI 범죄 대응 범부처 협의체 출범</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4124,32 +4124,32 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>359</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>7681</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4181,32 +4181,32 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
+          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4216,54 +4216,54 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>2754</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
+          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4273,54 +4273,54 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>358</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>11169</t>
+          <t>7681</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4352,32 +4352,32 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>357</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>13472</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4409,32 +4409,32 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>356</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>9023</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4466,55 +4466,226 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>352</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>개인정보보호정책과</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>11169</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>354</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>조사총괄과</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>13472</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>신기술개인정보과</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>9724</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>353</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>「개인정보 처리 방법에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12127</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="E75" t="inlineStr">
         <is>
           <t>전략기획팀</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
         <is>
           <t>11519</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t>공지사항</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
+      <c r="J75" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
+      <c r="K75" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>

--- a/docs/snapshot/downloads/pipc.xlsx
+++ b/docs/snapshot/downloads/pipc.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K75"/>
+  <dimension ref="A1:K76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,27 +476,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>45663</t>
+          <t>46031</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>383</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
+          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -511,49 +511,49 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-08-27 11:00:26.295039+09:00</t>
+          <t>2026-08-27 15:31:06.679425+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-27 11:00:26.295039+09:00</t>
+          <t>2026-08-27 15:31:06.679425+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>45662</t>
+          <t>45663</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
+          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -590,27 +590,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>45661</t>
+          <t>45662</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
+          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -647,32 +647,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>44101</t>
+          <t>45661</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>정부, 공공부문 개인정보 보호 역량 강화 위한 인력 확충한다</t>
+          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -692,34 +692,34 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-08-25 12:00:28.630385+09:00</t>
+          <t>2026-08-27 11:00:26.295039+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-08-25 12:00:28.630385+09:00</t>
+          <t>2026-08-27 11:00:26.295039+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>43521</t>
+          <t>44101</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>개인정보위, 2026년 공공기관 개인정보 보호수준 평가단 위촉</t>
+          <t>정부, 공공부문 개인정보 보호 역량 강화 위한 인력 확충한다</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -749,39 +749,39 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-08-24 15:00:28.011868+09:00</t>
+          <t>2026-08-25 12:00:28.630385+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-08-24 15:00:28.011868+09:00</t>
+          <t>2026-08-25 12:00:28.630385+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>43452</t>
+          <t>43521</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
+          <t>개인정보위, 2026년 공공기관 개인정보 보호수준 평가단 위촉</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -796,44 +796,44 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-08-24 14:01:07.394147+09:00</t>
+          <t>2026-08-24 15:00:28.011868+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-08-24 14:01:07.394147+09:00</t>
+          <t>2026-08-24 15:00:28.011868+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>43451</t>
+          <t>43452</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>381</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
+          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -875,27 +875,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>43121</t>
+          <t>43451</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>382</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
+          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -915,49 +915,49 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-08-24 10:00:26.766249+09:00</t>
+          <t>2026-08-24 14:01:07.394147+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-08-24 10:00:26.766249+09:00</t>
+          <t>2026-08-24 14:01:07.394147+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>40381</t>
+          <t>43121</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>안전한 인공지능 개발을 위한 개인정보 활용 특례 신설 「개인정보 보호법」 개정안 국회 본회의 통과</t>
+          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -977,44 +977,44 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-08-20 16:45:27.227566+09:00</t>
+          <t>2026-08-24 10:00:26.766249+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-08-20 16:45:27.227566+09:00</t>
+          <t>2026-08-24 10:00:26.766249+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>39131</t>
+          <t>40381</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>(대법원) 스크래핑 차단 한시적 유예 신청(~8.31.) 안내</t>
+          <t>안전한 인공지능 개발을 위한 개인정보 활용 특례 신설 「개인정보 보호법」 개정안 국회 본회의 통과</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1024,54 +1024,54 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-08-19 11:16:06.252027+09:00</t>
+          <t>2026-08-20 16:45:27.227566+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-08-19 11:16:06.252027+09:00</t>
+          <t>2026-08-20 16:45:27.227566+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>35591</t>
+          <t>39131</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>380</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
+          <t>(대법원) 스크래핑 차단 한시적 유예 신청(~8.31.) 안내</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1091,19 +1091,19 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-08-14 18:16:08.177242+09:00</t>
+          <t>2026-08-19 11:16:06.252027+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-08-14 18:16:08.177242+09:00</t>
+          <t>2026-08-19 11:16:06.252027+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>34711</t>
+          <t>35591</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1113,22 +1113,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>「국경 간 개인정보 보호 규칙 인증제도의 운영에 관한 지침」 일부개정안 행정예고</t>
+          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1148,39 +1148,39 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-08-13 17:31:09.311303+09:00</t>
+          <t>2026-08-14 18:16:08.177242+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-08-13 17:31:09.311303+09:00</t>
+          <t>2026-08-14 18:16:08.177242+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>34691</t>
+          <t>34711</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>379</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
+          <t>「국경 간 개인정보 보호 규칙 인증제도의 운영에 관한 지침」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12375</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1190,12 +1190,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1205,39 +1205,39 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-08-13 17:16:11.373869+09:00</t>
+          <t>2026-08-13 17:31:09.311303+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-08-13 17:16:11.373869+09:00</t>
+          <t>2026-08-13 17:31:09.311303+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>34071</t>
+          <t>34691</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>378</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
+          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12375</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1262,44 +1262,44 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:08.209725+09:00</t>
+          <t>2026-08-13 17:16:11.373869+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:08.209725+09:00</t>
+          <t>2026-08-13 17:16:11.373869+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>32571</t>
+          <t>34071</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>377</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
+          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1319,39 +1319,39 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-08-11 11:16:08.723253+09:00</t>
+          <t>2026-08-13 09:31:08.209725+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-08-11 11:16:08.723253+09:00</t>
+          <t>2026-08-13 09:31:08.209725+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>32541</t>
+          <t>32571</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>376</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1366,106 +1366,106 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-08-11 11:00:26.976860+09:00</t>
+          <t>2026-08-11 11:16:08.723253+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-08-11 11:00:26.976860+09:00</t>
+          <t>2026-08-11 11:16:08.723253+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>28831</t>
+          <t>32541</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제